--- a/Data/National Accounts/PSA-Quarter-Q1-1981-to-latest.xlsx
+++ b/Data/National Accounts/PSA-Quarter-Q1-1981-to-latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP 1981 and 1946 series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP 1981 and 1946 series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3D8284-EA1A-4AB1-8553-D972B333C740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE49FFD-230A-4DE1-A59E-A0D6629F1E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="721" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="721" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1981" sheetId="5" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="87">
   <si>
     <t>Source: Philippine Statistics Authority</t>
   </si>
@@ -229,13 +229,13 @@
     <t>3. Services</t>
   </si>
   <si>
-    <t>Q1 1981 to Q4 2025</t>
+    <t>Q1 1981 to Q1 2026</t>
   </si>
   <si>
-    <t>Q1 1982 to Q4 2025</t>
+    <t>Q1 1982 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
   </si>
   <si>
     <t>1981 - 1982</t>
@@ -369,6 +369,9 @@
   <si>
     <t>2024 - 2025</t>
   </si>
+  <si>
+    <t>2025 - 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -494,7 +497,21 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{615DD287-F4E0-4CDD-9CC4-94A5A163DEE0}"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -860,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FY304"/>
+  <dimension ref="A1:GC304"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50.5703125" style="1" customWidth="1"/>
@@ -987,41 +1004,42 @@
     <col min="162" max="162" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="163" max="164" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="165" max="165" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="166" max="181" width="15" style="1" customWidth="1"/>
-    <col min="182" max="16384" width="9.28515625" style="1"/>
+    <col min="166" max="182" width="15" style="1" customWidth="1"/>
+    <col min="183" max="185" width="15" style="1" hidden="1" customWidth="1"/>
+    <col min="186" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="5">
         <v>1981</v>
@@ -1293,8 +1311,14 @@
       <c r="FW9" s="5"/>
       <c r="FX9" s="5"/>
       <c r="FY9" s="5"/>
+      <c r="FZ9" s="5">
+        <v>2026</v>
+      </c>
+      <c r="GA9" s="5"/>
+      <c r="GB9" s="5"/>
+      <c r="GC9" s="5"/>
     </row>
-    <row r="10" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1838,8 +1862,20 @@
       <c r="FY10" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC10" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="12" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -2383,8 +2419,20 @@
       <c r="FY12" s="6">
         <v>6043627.9269005563</v>
       </c>
+      <c r="FZ12" s="6">
+        <v>5452905.1588575263</v>
+      </c>
+      <c r="GA12" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB12" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC12" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
@@ -2928,8 +2976,20 @@
       <c r="FY13" s="6">
         <v>1059964.9227690715</v>
       </c>
+      <c r="FZ13" s="6">
+        <v>1057919.7254915542</v>
+      </c>
+      <c r="GA13" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB13" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC13" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3533,20 @@
       <c r="FY14" s="6">
         <v>1455570.2933898694</v>
       </c>
+      <c r="FZ14" s="6">
+        <v>1450530.0602415975</v>
+      </c>
+      <c r="GA14" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB14" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC14" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -4018,8 +4090,20 @@
       <c r="FY15" s="6">
         <v>1994661.2692439985</v>
       </c>
+      <c r="FZ15" s="6">
+        <v>2067891.5134642548</v>
+      </c>
+      <c r="GA15" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB15" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC15" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -4563,8 +4647,20 @@
       <c r="FY16" s="6">
         <v>2693583.9508949714</v>
       </c>
+      <c r="FZ16" s="6">
+        <v>3111449.2745340024</v>
+      </c>
+      <c r="GA16" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB16" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC16" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
@@ -5108,8 +5204,20 @@
       <c r="FY17" s="6">
         <v>46899.07625182718</v>
       </c>
+      <c r="FZ17" s="6">
+        <v>16134.475405740552</v>
+      </c>
+      <c r="GA17" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB17" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC17" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:185" x14ac:dyDescent="0.2">
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -5290,8 +5398,12 @@
       <c r="FW18" s="6"/>
       <c r="FX18" s="6"/>
       <c r="FY18" s="6"/>
+      <c r="FZ18" s="6"/>
+      <c r="GA18" s="6"/>
+      <c r="GB18" s="6"/>
+      <c r="GC18" s="6"/>
     </row>
-    <row r="19" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>10</v>
       </c>
@@ -5835,12 +5947,24 @@
       <c r="FY19" s="6">
         <v>7907139.537660352</v>
       </c>
+      <c r="FZ19" s="6">
+        <v>6933931.6589266723</v>
+      </c>
+      <c r="GA19" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB19" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC19" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6022,43 +6146,47 @@
       <c r="FW24" s="8"/>
       <c r="FX24" s="8"/>
       <c r="FY24" s="8"/>
+      <c r="FZ24" s="8"/>
+      <c r="GA24" s="8"/>
+      <c r="GB24" s="8"/>
+      <c r="GC24" s="8"/>
     </row>
-    <row r="25" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="5">
         <v>1981</v>
@@ -6330,8 +6458,14 @@
       <c r="FW36" s="5"/>
       <c r="FX36" s="5"/>
       <c r="FY36" s="5"/>
+      <c r="FZ36" s="5">
+        <v>2025</v>
+      </c>
+      <c r="GA36" s="5"/>
+      <c r="GB36" s="5"/>
+      <c r="GC36" s="5"/>
     </row>
-    <row r="37" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
@@ -6875,8 +7009,20 @@
       <c r="FY37" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC37" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="39" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>1</v>
       </c>
@@ -7420,8 +7566,20 @@
       <c r="FY39" s="6">
         <v>4805972.1092409659</v>
       </c>
+      <c r="FZ39" s="6">
+        <v>4192515.5066607129</v>
+      </c>
+      <c r="GA39" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB39" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC39" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>2</v>
       </c>
@@ -7965,8 +8123,20 @@
       <c r="FY40" s="6">
         <v>770647.30893361906</v>
       </c>
+      <c r="FZ40" s="6">
+        <v>916516.90179032064</v>
+      </c>
+      <c r="GA40" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB40" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC40" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>3</v>
       </c>
@@ -8496,7 +8666,7 @@
         <v>1219734.0736893057</v>
       </c>
       <c r="FU41" s="6">
-        <v>1396158.3555608727</v>
+        <v>1396158.3555608722</v>
       </c>
       <c r="FV41" s="6">
         <v>1204282.1346572891</v>
@@ -8510,8 +8680,20 @@
       <c r="FY41" s="6">
         <v>1265208.0699194246</v>
       </c>
+      <c r="FZ41" s="6">
+        <v>1164109.6302006533</v>
+      </c>
+      <c r="GA41" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB41" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC41" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
@@ -9055,8 +9237,20 @@
       <c r="FY42" s="6">
         <v>1629144.7244439216</v>
       </c>
+      <c r="FZ42" s="6">
+        <v>1713777.8223234387</v>
+      </c>
+      <c r="GA42" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB42" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC42" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -9600,8 +9794,20 @@
       <c r="FY43" s="6">
         <v>2103560.8293640027</v>
       </c>
+      <c r="FZ43" s="6">
+        <v>2374729.9355641338</v>
+      </c>
+      <c r="GA43" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB43" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC43" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
@@ -10131,7 +10337,7 @@
         <v>34200.353967191651</v>
       </c>
       <c r="FU44" s="6">
-        <v>2955.3435315685347</v>
+        <v>2955.3435315703973</v>
       </c>
       <c r="FV44" s="6">
         <v>-25203.467436638661</v>
@@ -10145,8 +10351,20 @@
       <c r="FY44" s="6">
         <v>14845.693796754815</v>
       </c>
+      <c r="FZ44" s="6">
+        <v>14771.212075891905</v>
+      </c>
+      <c r="GA44" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB44" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC44" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:185" x14ac:dyDescent="0.2">
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -10327,8 +10545,12 @@
       <c r="FW45" s="6"/>
       <c r="FX45" s="6"/>
       <c r="FY45" s="6"/>
+      <c r="FZ45" s="6"/>
+      <c r="GA45" s="6"/>
+      <c r="GB45" s="6"/>
+      <c r="GC45" s="6"/>
     </row>
-    <row r="46" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
         <v>10</v>
       </c>
@@ -10872,12 +11094,24 @@
       <c r="FY46" s="6">
         <v>6382257.0769706834</v>
       </c>
+      <c r="FZ46" s="6">
+        <v>5626961.1374868834</v>
+      </c>
+      <c r="GA46" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB46" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC46" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -11059,48 +11293,56 @@
       <c r="FW51" s="8"/>
       <c r="FX51" s="8"/>
       <c r="FY51" s="8"/>
+      <c r="FZ51" s="8"/>
+      <c r="GA51" s="8"/>
+      <c r="GB51" s="8"/>
+      <c r="GC51" s="8"/>
     </row>
-    <row r="52" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>40</v>
       </c>
       <c r="FU60"/>
       <c r="FV60"/>
       <c r="FW60"/>
+      <c r="FZ60"/>
+      <c r="GA60"/>
     </row>
-    <row r="61" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
       <c r="FV61"/>
       <c r="FW61"/>
+      <c r="FZ61"/>
+      <c r="GA61"/>
     </row>
-    <row r="62" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
@@ -11227,10 +11469,11 @@
       <c r="FL62" s="8"/>
       <c r="FP62" s="8"/>
       <c r="FT62" s="8"/>
-      <c r="FV62"/>
       <c r="FW62"/>
+      <c r="FZ62"/>
+      <c r="GA62"/>
     </row>
-    <row r="63" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
       <c r="B63" s="5" t="s">
         <v>42</v>
@@ -11496,10 +11739,14 @@
       <c r="FS63" s="5"/>
       <c r="FT63" s="5"/>
       <c r="FU63" s="5"/>
-      <c r="FV63"/>
+      <c r="FV63" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="FW63"/>
+      <c r="FZ63"/>
+      <c r="GA63"/>
     </row>
-    <row r="64" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>14</v>
       </c>
@@ -12031,10 +12278,14 @@
       <c r="FU64" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="FV64"/>
+      <c r="FV64" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="FW64"/>
+      <c r="FZ64"/>
+      <c r="GA64"/>
     </row>
-    <row r="65" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B65" s="9"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -12208,10 +12459,12 @@
       <c r="FR65" s="9"/>
       <c r="FS65" s="9"/>
       <c r="FU65" s="4"/>
-      <c r="FV65"/>
+      <c r="FV65" s="9"/>
       <c r="FW65"/>
+      <c r="FZ65"/>
+      <c r="GA65"/>
     </row>
-    <row r="66" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>1</v>
       </c>
@@ -12743,10 +12996,14 @@
       <c r="FU66" s="11">
         <v>5.4505627561364491</v>
       </c>
-      <c r="FV66"/>
+      <c r="FV66" s="11">
+        <v>5.8501992776329246</v>
+      </c>
       <c r="FW66"/>
+      <c r="FZ66"/>
+      <c r="GA66"/>
     </row>
-    <row r="67" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>2</v>
       </c>
@@ -13278,10 +13535,14 @@
       <c r="FU67" s="11">
         <v>2.8913601244164227</v>
       </c>
-      <c r="FV67"/>
+      <c r="FV67" s="11">
+        <v>7.9445657207995168</v>
+      </c>
       <c r="FW67"/>
+      <c r="FZ67"/>
+      <c r="GA67"/>
     </row>
-    <row r="68" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -13813,10 +14074,14 @@
       <c r="FU68" s="11">
         <v>-10.329177002742313</v>
       </c>
-      <c r="FV68"/>
+      <c r="FV68" s="11">
+        <v>-1.1473611227701355</v>
+      </c>
       <c r="FW68"/>
+      <c r="FZ68"/>
+      <c r="GA68"/>
     </row>
-    <row r="69" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>4</v>
       </c>
@@ -14348,10 +14613,14 @@
       <c r="FU69" s="11">
         <v>14.357164947053874</v>
       </c>
-      <c r="FV69"/>
+      <c r="FV69" s="11">
+        <v>11.005065248055914</v>
+      </c>
       <c r="FW69"/>
+      <c r="FZ69"/>
+      <c r="GA69"/>
     </row>
-    <row r="70" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -14883,10 +15152,14 @@
       <c r="FU70" s="11">
         <v>3.953309514959912</v>
       </c>
-      <c r="FV70"/>
+      <c r="FV70" s="11">
+        <v>8.8774754111588692</v>
+      </c>
       <c r="FW70"/>
+      <c r="FZ70"/>
+      <c r="GA70"/>
     </row>
-    <row r="71" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
@@ -15063,10 +15336,12 @@
       <c r="FS71" s="11"/>
       <c r="FT71" s="11"/>
       <c r="FU71" s="11"/>
-      <c r="FV71"/>
+      <c r="FV71" s="11"/>
       <c r="FW71"/>
+      <c r="FZ71"/>
+      <c r="GA71"/>
     </row>
-    <row r="72" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
@@ -15243,10 +15518,12 @@
       <c r="FS72" s="11"/>
       <c r="FT72" s="11"/>
       <c r="FU72" s="11"/>
-      <c r="FV72"/>
+      <c r="FV72" s="11"/>
       <c r="FW72"/>
+      <c r="FZ72"/>
+      <c r="GA72"/>
     </row>
-    <row r="73" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>10</v>
       </c>
@@ -15778,26 +16055,34 @@
       <c r="FU73" s="11">
         <v>4.3231271264010616</v>
       </c>
-      <c r="FV73"/>
+      <c r="FV73" s="11">
+        <v>5.3235350852525869</v>
+      </c>
       <c r="FW73"/>
+      <c r="FZ73"/>
+      <c r="GA73"/>
     </row>
-    <row r="74" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV74"/>
+    <row r="74" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW74"/>
+      <c r="FZ74"/>
+      <c r="GA74"/>
     </row>
-    <row r="75" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV75"/>
+    <row r="75" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW75"/>
+      <c r="FZ75"/>
+      <c r="GA75"/>
     </row>
-    <row r="76" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV76"/>
+    <row r="76" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW76"/>
+      <c r="FZ76"/>
+      <c r="GA76"/>
     </row>
-    <row r="77" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV77"/>
+    <row r="77" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW77"/>
+      <c r="FZ77"/>
+      <c r="GA77"/>
     </row>
-    <row r="78" spans="1:179" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:183" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -15972,77 +16257,89 @@
       <c r="FR78" s="8"/>
       <c r="FS78" s="8"/>
       <c r="FT78" s="8"/>
-      <c r="FV78"/>
+      <c r="FV78" s="8"/>
       <c r="FW78"/>
+      <c r="FZ78"/>
+      <c r="GA78"/>
     </row>
-    <row r="79" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>0</v>
       </c>
       <c r="FM79" s="4"/>
       <c r="FQ79" s="4"/>
       <c r="FU79" s="4"/>
-      <c r="FV79"/>
       <c r="FW79"/>
+      <c r="FZ79"/>
+      <c r="GA79"/>
     </row>
-    <row r="80" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="FV80"/>
       <c r="FW80"/>
+      <c r="FZ80"/>
+      <c r="GA80"/>
     </row>
-    <row r="81" spans="1:179" ht="15" x14ac:dyDescent="0.25">
-      <c r="FV81"/>
+    <row r="81" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="FW81"/>
+      <c r="FZ81"/>
+      <c r="GA81"/>
     </row>
-    <row r="82" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="FV82"/>
       <c r="FW82"/>
+      <c r="FZ82"/>
+      <c r="GA82"/>
     </row>
-    <row r="83" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="FV83"/>
       <c r="FW83"/>
+      <c r="FZ83"/>
+      <c r="GA83"/>
     </row>
-    <row r="84" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="FV84"/>
       <c r="FW84"/>
+      <c r="FZ84"/>
+      <c r="GA84"/>
     </row>
-    <row r="85" spans="1:179" ht="15" x14ac:dyDescent="0.25">
-      <c r="FV85"/>
+    <row r="85" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="FW85"/>
+      <c r="FZ85"/>
+      <c r="GA85"/>
     </row>
-    <row r="86" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="FV86"/>
       <c r="FW86"/>
+      <c r="FZ86"/>
+      <c r="GA86"/>
     </row>
-    <row r="87" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="FV87"/>
       <c r="FW87"/>
+      <c r="FZ87"/>
+      <c r="GA87"/>
     </row>
-    <row r="88" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="FV88"/>
       <c r="FW88"/>
+      <c r="FZ88"/>
+      <c r="GA88"/>
     </row>
-    <row r="89" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="F89" s="8"/>
@@ -16125,10 +16422,11 @@
       <c r="FC89" s="8"/>
       <c r="FF89" s="8"/>
       <c r="FG89" s="8"/>
-      <c r="FV89"/>
       <c r="FW89"/>
+      <c r="FZ89"/>
+      <c r="GA89"/>
     </row>
-    <row r="90" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="5" t="s">
         <v>42</v>
@@ -16394,10 +16692,14 @@
       <c r="FS90" s="5"/>
       <c r="FT90" s="5"/>
       <c r="FU90" s="5"/>
-      <c r="FV90"/>
+      <c r="FV90" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="FW90"/>
+      <c r="FZ90"/>
+      <c r="GA90"/>
     </row>
-    <row r="91" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>14</v>
       </c>
@@ -16929,10 +17231,14 @@
       <c r="FU91" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="FV91"/>
+      <c r="FV91" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="FW91"/>
+      <c r="FZ91"/>
+      <c r="GA91"/>
     </row>
-    <row r="92" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
@@ -17106,10 +17412,12 @@
       <c r="FR92" s="9"/>
       <c r="FS92" s="9"/>
       <c r="FU92" s="4"/>
-      <c r="FV92"/>
+      <c r="FV92" s="9"/>
       <c r="FW92"/>
+      <c r="FZ92"/>
+      <c r="GA92"/>
     </row>
-    <row r="93" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>1</v>
       </c>
@@ -17641,10 +17949,14 @@
       <c r="FU93" s="11">
         <v>3.7778645631406675</v>
       </c>
-      <c r="FV93"/>
+      <c r="FV93" s="11">
+        <v>3.0158187478206173</v>
+      </c>
       <c r="FW93"/>
+      <c r="FZ93"/>
+      <c r="GA93"/>
     </row>
-    <row r="94" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>2</v>
       </c>
@@ -18176,10 +18488,14 @@
       <c r="FU94" s="11">
         <v>0.66249908974226912</v>
       </c>
-      <c r="FV94"/>
+      <c r="FV94" s="11">
+        <v>4.8204556176628444</v>
+      </c>
       <c r="FW94"/>
+      <c r="FZ94"/>
+      <c r="GA94"/>
     </row>
-    <row r="95" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>3</v>
       </c>
@@ -18697,7 +19013,7 @@
         <v>12.727259964515696</v>
       </c>
       <c r="FQ95" s="11">
-        <v>5.8352458755950778</v>
+        <v>5.8352458755950494</v>
       </c>
       <c r="FR95" s="11">
         <v>4.5199227468538936</v>
@@ -18709,12 +19025,16 @@
         <v>-1.9509253624586052</v>
       </c>
       <c r="FU95" s="11">
-        <v>-9.379329008050945</v>
-      </c>
-      <c r="FV95"/>
+        <v>-9.3793290080509166</v>
+      </c>
+      <c r="FV95" s="11">
+        <v>-3.3358050659838057</v>
+      </c>
       <c r="FW95"/>
+      <c r="FZ95"/>
+      <c r="GA95"/>
     </row>
-    <row r="96" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>4</v>
       </c>
@@ -19246,10 +19566,14 @@
       <c r="FU96" s="11">
         <v>13.331483611044789</v>
       </c>
-      <c r="FV96"/>
+      <c r="FV96" s="11">
+        <v>7.785515528806954</v>
+      </c>
       <c r="FW96"/>
+      <c r="FZ96"/>
+      <c r="GA96"/>
     </row>
-    <row r="97" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -19781,10 +20105,14 @@
       <c r="FU97" s="11">
         <v>3.2284956644134581</v>
       </c>
-      <c r="FV97"/>
+      <c r="FV97" s="11">
+        <v>6.1432002062635149</v>
+      </c>
       <c r="FW97"/>
+      <c r="FZ97"/>
+      <c r="GA97"/>
     </row>
-    <row r="98" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
@@ -19961,10 +20289,12 @@
       <c r="FS98" s="11"/>
       <c r="FT98" s="11"/>
       <c r="FU98" s="11"/>
-      <c r="FV98"/>
+      <c r="FV98" s="11"/>
       <c r="FW98"/>
+      <c r="FZ98"/>
+      <c r="GA98"/>
     </row>
-    <row r="99" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
@@ -20141,10 +20471,12 @@
       <c r="FS99" s="11"/>
       <c r="FT99" s="11"/>
       <c r="FU99" s="11"/>
-      <c r="FV99"/>
+      <c r="FV99" s="11"/>
       <c r="FW99"/>
+      <c r="FZ99"/>
+      <c r="GA99"/>
     </row>
-    <row r="100" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>10</v>
       </c>
@@ -20676,26 +21008,34 @@
       <c r="FU100" s="11">
         <v>3.0153928557466827</v>
       </c>
-      <c r="FV100"/>
+      <c r="FV100" s="11">
+        <v>2.7581741121167624</v>
+      </c>
       <c r="FW100"/>
+      <c r="FZ100"/>
+      <c r="GA100"/>
     </row>
-    <row r="101" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV101"/>
+    <row r="101" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW101"/>
+      <c r="FZ101"/>
+      <c r="GA101"/>
     </row>
-    <row r="102" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV102"/>
+    <row r="102" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW102"/>
+      <c r="FZ102"/>
+      <c r="GA102"/>
     </row>
-    <row r="103" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV103"/>
+    <row r="103" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW103"/>
+      <c r="FZ103"/>
+      <c r="GA103"/>
     </row>
-    <row r="104" spans="1:179" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV104"/>
+    <row r="104" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW104"/>
+      <c r="FZ104"/>
+      <c r="GA104"/>
     </row>
-    <row r="105" spans="1:179" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:183" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -20867,10 +21207,12 @@
       <c r="FO105" s="8"/>
       <c r="FR105" s="8"/>
       <c r="FS105" s="8"/>
-      <c r="FV105"/>
+      <c r="FV105" s="8"/>
       <c r="FW105"/>
+      <c r="FZ105"/>
+      <c r="GA105"/>
     </row>
-    <row r="106" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>0</v>
       </c>
@@ -20880,51 +21222,56 @@
       <c r="FQ106" s="4"/>
       <c r="FT106" s="4"/>
       <c r="FU106" s="4"/>
-      <c r="FV106"/>
       <c r="FW106"/>
+      <c r="FZ106"/>
+      <c r="GA106"/>
     </row>
-    <row r="107" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>21</v>
       </c>
       <c r="FV107"/>
       <c r="FW107"/>
+      <c r="FZ107"/>
+      <c r="GA107"/>
     </row>
-    <row r="108" spans="1:179" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="FV108"/>
       <c r="FW108"/>
+      <c r="FZ108"/>
+      <c r="GA108"/>
     </row>
-    <row r="109" spans="1:179" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:183" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:179" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:183" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:179" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:183" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="113" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="115" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="117" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="5">
         <v>1981</v>
@@ -21196,8 +21543,14 @@
       <c r="FW117" s="5"/>
       <c r="FX117" s="5"/>
       <c r="FY117" s="5"/>
+      <c r="FZ117" s="5">
+        <v>2025</v>
+      </c>
+      <c r="GA117" s="5"/>
+      <c r="GB117" s="5"/>
+      <c r="GC117" s="5"/>
     </row>
-    <row r="118" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>14</v>
       </c>
@@ -21741,8 +22094,20 @@
       <c r="FY118" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ118" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA118" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC118" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="120" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>1</v>
       </c>
@@ -22286,8 +22651,20 @@
       <c r="FY120" s="11">
         <v>76.432544260990852</v>
       </c>
+      <c r="FZ120" s="11">
+        <v>78.640884091170875</v>
+      </c>
+      <c r="GA120" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB120" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC120" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="121" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>2</v>
       </c>
@@ -22831,8 +23208,20 @@
       <c r="FY121" s="11">
         <v>13.405162735786311</v>
       </c>
+      <c r="FZ121" s="11">
+        <v>15.257140934315371</v>
+      </c>
+      <c r="GA121" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB121" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC121" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="122" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>3</v>
       </c>
@@ -23376,8 +23765,20 @@
       <c r="FY122" s="11">
         <v>18.408304121322729</v>
       </c>
+      <c r="FZ122" s="11">
+        <v>20.919301365974672</v>
+      </c>
+      <c r="GA122" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB122" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC122" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="123" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>4</v>
       </c>
@@ -23921,8 +24322,20 @@
       <c r="FY123" s="11">
         <v>25.226079035835504</v>
       </c>
+      <c r="FZ123" s="11">
+        <v>29.822784751592877</v>
+      </c>
+      <c r="GA123" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB123" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC123" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="124" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -24466,8 +24879,20 @@
       <c r="FY124" s="11">
         <v>34.065213318493903</v>
       </c>
+      <c r="FZ124" s="11">
+        <v>44.872799842616772</v>
+      </c>
+      <c r="GA124" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB124" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC124" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="125" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:185" x14ac:dyDescent="0.2">
       <c r="B125" s="11"/>
       <c r="C125" s="11"/>
       <c r="D125" s="11"/>
@@ -24648,8 +25073,12 @@
       <c r="FW125" s="11"/>
       <c r="FX125" s="11"/>
       <c r="FY125" s="11"/>
+      <c r="FZ125" s="11"/>
+      <c r="GA125" s="11"/>
+      <c r="GB125" s="11"/>
+      <c r="GC125" s="11"/>
     </row>
-    <row r="126" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:185" x14ac:dyDescent="0.2">
       <c r="B126" s="11"/>
       <c r="C126" s="11"/>
       <c r="D126" s="11"/>
@@ -24830,8 +25259,12 @@
       <c r="FW126" s="11"/>
       <c r="FX126" s="11"/>
       <c r="FY126" s="11"/>
+      <c r="FZ126" s="11"/>
+      <c r="GA126" s="11"/>
+      <c r="GB126" s="11"/>
+      <c r="GC126" s="11"/>
     </row>
-    <row r="127" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
         <v>10</v>
       </c>
@@ -25375,28 +25808,40 @@
       <c r="FY127" s="11">
         <v>100</v>
       </c>
+      <c r="FZ127" s="11">
+        <v>100</v>
+      </c>
+      <c r="GA127" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB127" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC127" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="128" spans="1:181" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:185" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B129" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B130" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B131" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -25578,43 +26023,47 @@
       <c r="FW132" s="8"/>
       <c r="FX132" s="8"/>
       <c r="FY132" s="8"/>
+      <c r="FZ132" s="8"/>
+      <c r="GA132" s="8"/>
+      <c r="GB132" s="8"/>
+      <c r="GC132" s="8"/>
     </row>
-    <row r="133" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="141" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="5">
         <v>1981</v>
@@ -25886,8 +26335,14 @@
       <c r="FW144" s="5"/>
       <c r="FX144" s="5"/>
       <c r="FY144" s="5"/>
+      <c r="FZ144" s="5">
+        <v>2025</v>
+      </c>
+      <c r="GA144" s="5"/>
+      <c r="GB144" s="5"/>
+      <c r="GC144" s="5"/>
     </row>
-    <row r="145" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>14</v>
       </c>
@@ -26431,8 +26886,20 @@
       <c r="FY145" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ145" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA145" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB145" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC145" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="147" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>1</v>
       </c>
@@ -26976,8 +27443,20 @@
       <c r="FY147" s="11">
         <v>75.302076542521604</v>
       </c>
+      <c r="FZ147" s="11">
+        <v>74.50763216987805</v>
+      </c>
+      <c r="GA147" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB147" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC147" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="148" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>2</v>
       </c>
@@ -27521,8 +28000,20 @@
       <c r="FY148" s="11">
         <v>12.074839663140052</v>
       </c>
+      <c r="FZ148" s="11">
+        <v>16.287955068402265</v>
+      </c>
+      <c r="GA148" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB148" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC148" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="149" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>3</v>
       </c>
@@ -28052,7 +28543,7 @@
         <v>22.941394414327114</v>
       </c>
       <c r="FU149" s="11">
-        <v>22.535256689347115</v>
+        <v>22.535256689347108</v>
       </c>
       <c r="FV149" s="11">
         <v>21.992302816666438</v>
@@ -28066,8 +28557,20 @@
       <c r="FY149" s="11">
         <v>19.823834337302365</v>
       </c>
+      <c r="FZ149" s="11">
+        <v>20.688069488259671</v>
+      </c>
+      <c r="GA149" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB149" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC149" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="150" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>4</v>
       </c>
@@ -28611,8 +29114,20 @@
       <c r="FY150" s="11">
         <v>25.526153283960003</v>
       </c>
+      <c r="FZ150" s="11">
+        <v>30.45654271372571</v>
+      </c>
+      <c r="GA150" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB150" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC150" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="151" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -29156,8 +29671,20 @@
       <c r="FY151" s="11">
         <v>32.959512661349123</v>
       </c>
+      <c r="FZ151" s="11">
+        <v>42.20270724358933</v>
+      </c>
+      <c r="GA151" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB151" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC151" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="152" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:185" x14ac:dyDescent="0.2">
       <c r="B152" s="11"/>
       <c r="C152" s="11"/>
       <c r="D152" s="11"/>
@@ -29338,8 +29865,12 @@
       <c r="FW152" s="11"/>
       <c r="FX152" s="11"/>
       <c r="FY152" s="11"/>
+      <c r="FZ152" s="11"/>
+      <c r="GA152" s="11"/>
+      <c r="GB152" s="11"/>
+      <c r="GC152" s="11"/>
     </row>
-    <row r="153" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:185" x14ac:dyDescent="0.2">
       <c r="B153" s="11"/>
       <c r="C153" s="11"/>
       <c r="D153" s="11"/>
@@ -29520,8 +30051,12 @@
       <c r="FW153" s="11"/>
       <c r="FX153" s="11"/>
       <c r="FY153" s="11"/>
+      <c r="FZ153" s="11"/>
+      <c r="GA153" s="11"/>
+      <c r="GB153" s="11"/>
+      <c r="GC153" s="11"/>
     </row>
-    <row r="154" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
         <v>10</v>
       </c>
@@ -30065,12 +30600,24 @@
       <c r="FY154" s="11">
         <v>100</v>
       </c>
+      <c r="FZ154" s="11">
+        <v>100</v>
+      </c>
+      <c r="GA154" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB154" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC154" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="155" spans="1:181" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:185" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -30252,43 +30799,47 @@
       <c r="FW159" s="8"/>
       <c r="FX159" s="8"/>
       <c r="FY159" s="8"/>
+      <c r="FZ159" s="8"/>
+      <c r="GA159" s="8"/>
+      <c r="GB159" s="8"/>
+      <c r="GC159" s="8"/>
     </row>
-    <row r="160" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="164" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="167" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="5">
         <v>1981</v>
@@ -30560,8 +31111,14 @@
       <c r="FW171" s="5"/>
       <c r="FX171" s="5"/>
       <c r="FY171" s="5"/>
+      <c r="FZ171" s="5">
+        <v>2025</v>
+      </c>
+      <c r="GA171" s="5"/>
+      <c r="GB171" s="5"/>
+      <c r="GC171" s="5"/>
     </row>
-    <row r="172" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>13</v>
       </c>
@@ -31105,8 +31662,20 @@
       <c r="FY172" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ172" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA172" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB172" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC172" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="174" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A174" s="12" t="s">
         <v>36</v>
       </c>
@@ -31650,8 +32219,20 @@
       <c r="FY174" s="6">
         <v>689711.94390111906</v>
       </c>
+      <c r="FZ174" s="6">
+        <v>618404.8468013861</v>
+      </c>
+      <c r="GA174" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB174" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC174" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="175" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="12" t="s">
         <v>37</v>
       </c>
@@ -32195,8 +32776,20 @@
       <c r="FY175" s="6">
         <v>2176719.5042936383</v>
       </c>
+      <c r="FZ175" s="6">
+        <v>1915723.8568371453</v>
+      </c>
+      <c r="GA175" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB175" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC175" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="176" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A176" s="12" t="s">
         <v>38</v>
       </c>
@@ -32740,8 +33333,20 @@
       <c r="FY176" s="6">
         <v>5040708.0894655949</v>
       </c>
+      <c r="FZ176" s="6">
+        <v>4399802.955288141</v>
+      </c>
+      <c r="GA176" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB176" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC176" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="177" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A177" s="14"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
@@ -32923,8 +33528,12 @@
       <c r="FW177" s="6"/>
       <c r="FX177" s="6"/>
       <c r="FY177" s="6"/>
+      <c r="FZ177" s="6"/>
+      <c r="GA177" s="6"/>
+      <c r="GB177" s="6"/>
+      <c r="GC177" s="6"/>
     </row>
-    <row r="178" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>10</v>
       </c>
@@ -33468,8 +34077,20 @@
       <c r="FY178" s="6">
         <v>7907139.537660352</v>
       </c>
+      <c r="FZ178" s="6">
+        <v>6933931.6589266723</v>
+      </c>
+      <c r="GA178" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB178" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC178" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="179" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB179" s="1">
         <v>20558.222744577564</v>
       </c>
@@ -33477,8 +34098,8 @@
         <v>-24370.119758612476</v>
       </c>
     </row>
-    <row r="180" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB181" s="1">
         <v>4422950.8840171499</v>
       </c>
@@ -33486,8 +34107,8 @@
         <v>4857262.3839106075</v>
       </c>
     </row>
-    <row r="182" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
@@ -33669,49 +34290,53 @@
       <c r="FW183" s="8"/>
       <c r="FX183" s="8"/>
       <c r="FY183" s="8"/>
+      <c r="FZ183" s="8"/>
+      <c r="GA183" s="8"/>
+      <c r="GB183" s="8"/>
+      <c r="GC183" s="8"/>
     </row>
-    <row r="184" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="190" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
     </row>
-    <row r="191" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="192" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="193" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
     </row>
-    <row r="195" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="5">
         <v>1981</v>
@@ -33983,8 +34608,14 @@
       <c r="FW195" s="5"/>
       <c r="FX195" s="5"/>
       <c r="FY195" s="5"/>
+      <c r="FZ195" s="5">
+        <v>2025</v>
+      </c>
+      <c r="GA195" s="5"/>
+      <c r="GB195" s="5"/>
+      <c r="GC195" s="5"/>
     </row>
-    <row r="196" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>13</v>
       </c>
@@ -34528,8 +35159,20 @@
       <c r="FY196" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ196" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA196" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB196" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC196" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="198" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A198" s="12" t="s">
         <v>36</v>
       </c>
@@ -35073,8 +35716,20 @@
       <c r="FY198" s="6">
         <v>528808.93452259735</v>
       </c>
+      <c r="FZ198" s="6">
+        <v>455741.24889463489</v>
+      </c>
+      <c r="GA198" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB198" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC198" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="199" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A199" s="12" t="s">
         <v>37</v>
       </c>
@@ -35618,8 +36273,20 @@
       <c r="FY199" s="6">
         <v>1826344.8260546725</v>
       </c>
+      <c r="FZ199" s="6">
+        <v>1616889.592773573</v>
+      </c>
+      <c r="GA199" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB199" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC199" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="200" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A200" s="12" t="s">
         <v>38</v>
       </c>
@@ -36163,8 +36830,20 @@
       <c r="FY200" s="6">
         <v>4027103.316393414</v>
       </c>
+      <c r="FZ200" s="6">
+        <v>3554330.2958186753</v>
+      </c>
+      <c r="GA200" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB200" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC200" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="201" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A201" s="14"/>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
@@ -36346,8 +37025,12 @@
       <c r="FW201" s="6"/>
       <c r="FX201" s="6"/>
       <c r="FY201" s="6"/>
+      <c r="FZ201" s="6"/>
+      <c r="GA201" s="6"/>
+      <c r="GB201" s="6"/>
+      <c r="GC201" s="6"/>
     </row>
-    <row r="202" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>10</v>
       </c>
@@ -36891,8 +37574,20 @@
       <c r="FY202" s="6">
         <v>6382257.0769706834</v>
       </c>
+      <c r="FZ202" s="6">
+        <v>5626961.1374868834</v>
+      </c>
+      <c r="GA202" s="6">
+        <v>0</v>
+      </c>
+      <c r="GB202" s="6">
+        <v>0</v>
+      </c>
+      <c r="GC202" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="203" spans="1:181" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:185" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="FB203" s="13">
         <v>20558.222744577564</v>
@@ -36912,8 +37607,11 @@
       <c r="FW203" s="1"/>
       <c r="FX203" s="1"/>
       <c r="FY203" s="1"/>
+      <c r="GA203" s="1"/>
+      <c r="GB203" s="1"/>
+      <c r="GC203" s="1"/>
     </row>
-    <row r="204" spans="1:181" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:185" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="FK204" s="1"/>
       <c r="FL204" s="1"/>
@@ -36927,8 +37625,11 @@
       <c r="FW204" s="1"/>
       <c r="FX204" s="1"/>
       <c r="FY204" s="1"/>
+      <c r="GA204" s="1"/>
+      <c r="GB204" s="1"/>
+      <c r="GC204" s="1"/>
     </row>
-    <row r="205" spans="1:181" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:185" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="FB205" s="13">
         <v>4422950.8840171499</v>
@@ -36948,8 +37649,11 @@
       <c r="FW205" s="1"/>
       <c r="FX205" s="1"/>
       <c r="FY205" s="1"/>
+      <c r="GA205" s="1"/>
+      <c r="GB205" s="1"/>
+      <c r="GC205" s="1"/>
     </row>
-    <row r="206" spans="1:181" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:185" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="FK206" s="1"/>
       <c r="FL206" s="1"/>
@@ -36963,8 +37667,11 @@
       <c r="FW206" s="1"/>
       <c r="FX206" s="1"/>
       <c r="FY206" s="1"/>
+      <c r="GA206" s="1"/>
+      <c r="GB206" s="1"/>
+      <c r="GC206" s="1"/>
     </row>
-    <row r="207" spans="1:181" s="13" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:185" s="13" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -37146,34 +37853,42 @@
       <c r="FW207" s="8"/>
       <c r="FX207" s="8"/>
       <c r="FY207" s="8"/>
+      <c r="FZ207" s="8"/>
+      <c r="GA207" s="8"/>
+      <c r="GB207" s="8"/>
+      <c r="GC207" s="8"/>
     </row>
-    <row r="208" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="214" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FV214"/>
       <c r="FW214"/>
       <c r="FX214"/>
       <c r="FY214"/>
+      <c r="FZ214"/>
+      <c r="GA214"/>
+      <c r="GB214"/>
+      <c r="GC214"/>
     </row>
-    <row r="215" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>30</v>
       </c>
@@ -37181,8 +37896,12 @@
       <c r="FW215"/>
       <c r="FX215"/>
       <c r="FY215"/>
+      <c r="FZ215"/>
+      <c r="GA215"/>
+      <c r="GB215"/>
+      <c r="GC215"/>
     </row>
-    <row r="216" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>40</v>
       </c>
@@ -37190,8 +37909,12 @@
       <c r="FW216"/>
       <c r="FX216"/>
       <c r="FY216"/>
+      <c r="FZ216"/>
+      <c r="GA216"/>
+      <c r="GB216"/>
+      <c r="GC216"/>
     </row>
-    <row r="217" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -37199,8 +37922,12 @@
       <c r="FW217"/>
       <c r="FX217"/>
       <c r="FY217"/>
+      <c r="FZ217"/>
+      <c r="GA217"/>
+      <c r="GB217"/>
+      <c r="GC217"/>
     </row>
-    <row r="218" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
       <c r="F218" s="8"/>
@@ -37286,12 +38013,15 @@
       <c r="FL218" s="8"/>
       <c r="FP218" s="8"/>
       <c r="FT218" s="8"/>
-      <c r="FV218"/>
       <c r="FW218"/>
       <c r="FX218"/>
       <c r="FY218"/>
+      <c r="FZ218"/>
+      <c r="GA218"/>
+      <c r="GB218"/>
+      <c r="GC218"/>
     </row>
-    <row r="219" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="4"/>
       <c r="B219" s="5" t="s">
         <v>42</v>
@@ -37557,12 +38287,18 @@
       <c r="FS219" s="5"/>
       <c r="FT219" s="5"/>
       <c r="FU219" s="5"/>
-      <c r="FV219"/>
+      <c r="FV219" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="FW219"/>
       <c r="FX219"/>
       <c r="FY219"/>
+      <c r="FZ219"/>
+      <c r="GA219"/>
+      <c r="GB219"/>
+      <c r="GC219"/>
     </row>
-    <row r="220" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>13</v>
       </c>
@@ -38094,12 +38830,18 @@
       <c r="FU220" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="FV220"/>
+      <c r="FV220" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="FW220"/>
       <c r="FX220"/>
       <c r="FY220"/>
+      <c r="FZ220"/>
+      <c r="GA220"/>
+      <c r="GB220"/>
+      <c r="GC220"/>
     </row>
-    <row r="221" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="B221" s="9"/>
       <c r="F221" s="9"/>
       <c r="J221" s="9"/>
@@ -38153,12 +38895,16 @@
       <c r="FS221" s="9"/>
       <c r="FT221" s="4"/>
       <c r="FU221" s="4"/>
-      <c r="FV221"/>
+      <c r="FV221" s="9"/>
       <c r="FW221"/>
       <c r="FX221"/>
       <c r="FY221"/>
+      <c r="FZ221"/>
+      <c r="GA221"/>
+      <c r="GB221"/>
+      <c r="GC221"/>
     </row>
-    <row r="222" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
         <v>36</v>
       </c>
@@ -38690,12 +39436,18 @@
       <c r="FU222" s="11">
         <v>-2.0499984234648139</v>
       </c>
-      <c r="FV222"/>
+      <c r="FV222" s="11">
+        <v>-1.3730581800920305</v>
+      </c>
       <c r="FW222"/>
       <c r="FX222"/>
       <c r="FY222"/>
+      <c r="FZ222"/>
+      <c r="GA222"/>
+      <c r="GB222"/>
+      <c r="GC222"/>
     </row>
-    <row r="223" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
         <v>37</v>
       </c>
@@ -39227,12 +39979,18 @@
       <c r="FU223" s="11">
         <v>0.6458671007052601</v>
       </c>
-      <c r="FV223"/>
+      <c r="FV223" s="11">
+        <v>3.2644679009770812</v>
+      </c>
       <c r="FW223"/>
       <c r="FX223"/>
       <c r="FY223"/>
+      <c r="FZ223"/>
+      <c r="GA223"/>
+      <c r="GB223"/>
+      <c r="GC223"/>
     </row>
-    <row r="224" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
         <v>38</v>
       </c>
@@ -39764,12 +40522,18 @@
       <c r="FU224" s="11">
         <v>6.9630053219279233</v>
       </c>
-      <c r="FV224"/>
+      <c r="FV224" s="11">
+        <v>7.2787195409626833</v>
+      </c>
       <c r="FW224"/>
       <c r="FX224"/>
       <c r="FY224"/>
+      <c r="FZ224"/>
+      <c r="GA224"/>
+      <c r="GB224"/>
+      <c r="GC224"/>
     </row>
-    <row r="225" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="14"/>
       <c r="B225" s="11"/>
       <c r="C225" s="11"/>
@@ -39947,12 +40711,16 @@
       <c r="FS225" s="11"/>
       <c r="FT225" s="11"/>
       <c r="FU225" s="11"/>
-      <c r="FV225"/>
+      <c r="FV225" s="11"/>
       <c r="FW225"/>
       <c r="FX225"/>
       <c r="FY225"/>
+      <c r="FZ225"/>
+      <c r="GA225"/>
+      <c r="GB225"/>
+      <c r="GC225"/>
     </row>
-    <row r="226" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>10</v>
       </c>
@@ -40484,12 +41252,18 @@
       <c r="FU226" s="11">
         <v>4.3231271264010616</v>
       </c>
-      <c r="FV226"/>
+      <c r="FV226" s="11">
+        <v>5.3235350852525869</v>
+      </c>
       <c r="FW226"/>
       <c r="FX226"/>
       <c r="FY226"/>
+      <c r="FZ226"/>
+      <c r="GA226"/>
+      <c r="GB226"/>
+      <c r="GC226"/>
     </row>
-    <row r="227" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" s="16"/>
       <c r="C227" s="16"/>
       <c r="D227" s="16"/>
@@ -40664,12 +41438,16 @@
       <c r="FO227" s="16"/>
       <c r="FR227" s="16"/>
       <c r="FS227" s="16"/>
-      <c r="FV227"/>
+      <c r="FV227" s="16"/>
       <c r="FW227"/>
       <c r="FX227"/>
       <c r="FY227"/>
+      <c r="FZ227"/>
+      <c r="GA227"/>
+      <c r="GB227"/>
+      <c r="GC227"/>
     </row>
-    <row r="228" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" s="16"/>
       <c r="C228" s="16"/>
       <c r="D228" s="16"/>
@@ -40844,12 +41622,16 @@
       <c r="FO228" s="16"/>
       <c r="FR228" s="16"/>
       <c r="FS228" s="16"/>
-      <c r="FV228"/>
+      <c r="FV228" s="16"/>
       <c r="FW228"/>
       <c r="FX228"/>
       <c r="FY228"/>
+      <c r="FZ228"/>
+      <c r="GA228"/>
+      <c r="GB228"/>
+      <c r="GC228"/>
     </row>
-    <row r="229" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" s="16"/>
       <c r="C229" s="16"/>
       <c r="D229" s="16"/>
@@ -41030,24 +41812,33 @@
         <v>14.6558695901769</v>
       </c>
       <c r="FS229" s="16"/>
-      <c r="FV229"/>
+      <c r="FV229" s="16">
+        <v>14.6558695901769</v>
+      </c>
       <c r="FW229"/>
       <c r="FX229"/>
       <c r="FY229"/>
+      <c r="FZ229"/>
+      <c r="GA229"/>
+      <c r="GB229"/>
+      <c r="GC229"/>
     </row>
-    <row r="230" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="EX230" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="EY230" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="FV230"/>
       <c r="FW230"/>
       <c r="FX230"/>
       <c r="FY230"/>
+      <c r="FZ230"/>
+      <c r="GA230"/>
+      <c r="GB230"/>
+      <c r="GC230"/>
     </row>
-    <row r="231" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8"/>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
@@ -41219,12 +42010,16 @@
       <c r="FO231" s="8"/>
       <c r="FR231" s="8"/>
       <c r="FS231" s="8"/>
-      <c r="FV231"/>
+      <c r="FV231" s="8"/>
       <c r="FW231"/>
       <c r="FX231"/>
       <c r="FY231"/>
+      <c r="FZ231"/>
+      <c r="GA231"/>
+      <c r="GB231"/>
+      <c r="GC231"/>
     </row>
-    <row r="232" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>0</v>
       </c>
@@ -41234,84 +42029,114 @@
       <c r="FQ232" s="4"/>
       <c r="FT232" s="4"/>
       <c r="FU232" s="4"/>
-      <c r="FV232"/>
       <c r="FW232"/>
       <c r="FX232"/>
       <c r="FY232"/>
+      <c r="FZ232"/>
+      <c r="GA232"/>
+      <c r="GB232"/>
+      <c r="GC232"/>
     </row>
-    <row r="233" spans="1:181" ht="15" x14ac:dyDescent="0.25">
-      <c r="FV233"/>
+    <row r="233" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FW233"/>
       <c r="FX233"/>
       <c r="FY233"/>
+      <c r="FZ233"/>
+      <c r="GA233"/>
+      <c r="GB233"/>
+      <c r="GC233"/>
     </row>
-    <row r="234" spans="1:181" ht="15" x14ac:dyDescent="0.25">
-      <c r="FV234"/>
+    <row r="234" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FW234"/>
       <c r="FX234"/>
       <c r="FY234"/>
+      <c r="FZ234"/>
+      <c r="GA234"/>
+      <c r="GB234"/>
+      <c r="GC234"/>
     </row>
-    <row r="235" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="FV235"/>
       <c r="FW235"/>
       <c r="FX235"/>
       <c r="FY235"/>
+      <c r="FZ235"/>
+      <c r="GA235"/>
+      <c r="GB235"/>
+      <c r="GC235"/>
     </row>
-    <row r="236" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="FV236"/>
       <c r="FW236"/>
       <c r="FX236"/>
       <c r="FY236"/>
+      <c r="FZ236"/>
+      <c r="GA236"/>
+      <c r="GB236"/>
+      <c r="GC236"/>
     </row>
-    <row r="237" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="FV237"/>
       <c r="FW237"/>
       <c r="FX237"/>
       <c r="FY237"/>
+      <c r="FZ237"/>
+      <c r="GA237"/>
+      <c r="GB237"/>
+      <c r="GC237"/>
     </row>
-    <row r="238" spans="1:181" ht="15" x14ac:dyDescent="0.25">
-      <c r="FV238"/>
+    <row r="238" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FW238"/>
       <c r="FX238"/>
       <c r="FY238"/>
+      <c r="FZ238"/>
+      <c r="GA238"/>
+      <c r="GB238"/>
+      <c r="GC238"/>
     </row>
-    <row r="239" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="FV239"/>
       <c r="FW239"/>
       <c r="FX239"/>
       <c r="FY239"/>
+      <c r="FZ239"/>
+      <c r="GA239"/>
+      <c r="GB239"/>
+      <c r="GC239"/>
     </row>
-    <row r="240" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="FV240"/>
       <c r="FW240"/>
       <c r="FX240"/>
       <c r="FY240"/>
+      <c r="FZ240"/>
+      <c r="GA240"/>
+      <c r="GB240"/>
+      <c r="GC240"/>
     </row>
-    <row r="241" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="FV241"/>
       <c r="FW241"/>
       <c r="FX241"/>
       <c r="FY241"/>
+      <c r="FZ241"/>
+      <c r="GA241"/>
+      <c r="GB241"/>
+      <c r="GC241"/>
     </row>
-    <row r="242" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
       <c r="F242" s="8"/>
@@ -41397,12 +42222,15 @@
       <c r="FL242" s="8"/>
       <c r="FP242" s="8"/>
       <c r="FT242" s="8"/>
-      <c r="FV242"/>
       <c r="FW242"/>
       <c r="FX242"/>
       <c r="FY242"/>
+      <c r="FZ242"/>
+      <c r="GA242"/>
+      <c r="GB242"/>
+      <c r="GC242"/>
     </row>
-    <row r="243" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="4"/>
       <c r="B243" s="5" t="s">
         <v>42</v>
@@ -41668,12 +42496,18 @@
       <c r="FS243" s="5"/>
       <c r="FT243" s="5"/>
       <c r="FU243" s="5"/>
-      <c r="FV243"/>
+      <c r="FV243" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="FW243"/>
       <c r="FX243"/>
       <c r="FY243"/>
+      <c r="FZ243"/>
+      <c r="GA243"/>
+      <c r="GB243"/>
+      <c r="GC243"/>
     </row>
-    <row r="244" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>13</v>
       </c>
@@ -42205,12 +43039,18 @@
       <c r="FU244" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="FV244"/>
+      <c r="FV244" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="FW244"/>
       <c r="FX244"/>
       <c r="FY244"/>
+      <c r="FZ244"/>
+      <c r="GA244"/>
+      <c r="GB244"/>
+      <c r="GC244"/>
     </row>
-    <row r="245" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="B245" s="9"/>
       <c r="F245" s="9"/>
       <c r="J245" s="9"/>
@@ -42261,12 +43101,16 @@
       <c r="FR245" s="9"/>
       <c r="FS245" s="9"/>
       <c r="FU245" s="4"/>
-      <c r="FV245"/>
+      <c r="FV245" s="9"/>
       <c r="FW245"/>
       <c r="FX245"/>
       <c r="FY245"/>
+      <c r="FZ245"/>
+      <c r="GA245"/>
+      <c r="GB245"/>
+      <c r="GC245"/>
     </row>
-    <row r="246" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
         <v>36</v>
       </c>
@@ -42798,12 +43642,18 @@
       <c r="FU246" s="11">
         <v>1.0256262320668554</v>
       </c>
-      <c r="FV246"/>
+      <c r="FV246" s="11">
+        <v>-0.20950936020631161</v>
+      </c>
       <c r="FW246"/>
       <c r="FX246"/>
       <c r="FY246"/>
+      <c r="FZ246"/>
+      <c r="GA246"/>
+      <c r="GB246"/>
+      <c r="GC246"/>
     </row>
-    <row r="247" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
         <v>37</v>
       </c>
@@ -43335,12 +44185,18 @@
       <c r="FU247" s="11">
         <v>-0.30910505893317008</v>
       </c>
-      <c r="FV247"/>
+      <c r="FV247" s="11">
+        <v>-5.0285569020928733E-2</v>
+      </c>
       <c r="FW247"/>
       <c r="FX247"/>
       <c r="FY247"/>
+      <c r="FZ247"/>
+      <c r="GA247"/>
+      <c r="GB247"/>
+      <c r="GC247"/>
     </row>
-    <row r="248" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
         <v>38</v>
       </c>
@@ -43872,12 +44728,18 @@
       <c r="FU248" s="11">
         <v>4.8726960835999478</v>
       </c>
-      <c r="FV248"/>
+      <c r="FV248" s="11">
+        <v>4.4922757672596987</v>
+      </c>
       <c r="FW248"/>
       <c r="FX248"/>
       <c r="FY248"/>
+      <c r="FZ248"/>
+      <c r="GA248"/>
+      <c r="GB248"/>
+      <c r="GC248"/>
     </row>
-    <row r="249" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="14"/>
       <c r="B249" s="11"/>
       <c r="C249" s="11"/>
@@ -44055,12 +44917,16 @@
       <c r="FS249" s="11"/>
       <c r="FT249" s="11"/>
       <c r="FU249" s="11"/>
-      <c r="FV249"/>
+      <c r="FV249" s="11"/>
       <c r="FW249"/>
       <c r="FX249"/>
       <c r="FY249"/>
+      <c r="FZ249"/>
+      <c r="GA249"/>
+      <c r="GB249"/>
+      <c r="GC249"/>
     </row>
-    <row r="250" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -44592,12 +45458,18 @@
       <c r="FU250" s="11">
         <v>3.0153928557466827</v>
       </c>
-      <c r="FV250"/>
+      <c r="FV250" s="11">
+        <v>2.7581741121167624</v>
+      </c>
       <c r="FW250"/>
       <c r="FX250"/>
       <c r="FY250"/>
+      <c r="FZ250"/>
+      <c r="GA250"/>
+      <c r="GB250"/>
+      <c r="GC250"/>
     </row>
-    <row r="251" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B251" s="16"/>
       <c r="C251" s="16"/>
       <c r="D251" s="16"/>
@@ -44772,12 +45644,16 @@
       <c r="FO251" s="16"/>
       <c r="FR251" s="16"/>
       <c r="FS251" s="16"/>
-      <c r="FV251"/>
+      <c r="FV251" s="16"/>
       <c r="FW251"/>
       <c r="FX251"/>
       <c r="FY251"/>
+      <c r="FZ251"/>
+      <c r="GA251"/>
+      <c r="GB251"/>
+      <c r="GC251"/>
     </row>
-    <row r="252" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B252" s="16"/>
       <c r="C252" s="16"/>
       <c r="D252" s="16"/>
@@ -44948,12 +45824,16 @@
       <c r="FO252" s="16"/>
       <c r="FR252" s="16"/>
       <c r="FS252" s="16"/>
-      <c r="FV252"/>
+      <c r="FV252" s="16"/>
       <c r="FW252"/>
       <c r="FX252"/>
       <c r="FY252"/>
+      <c r="FZ252"/>
+      <c r="GA252"/>
+      <c r="GB252"/>
+      <c r="GC252"/>
     </row>
-    <row r="253" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B253" s="16"/>
       <c r="C253" s="16"/>
       <c r="D253" s="16"/>
@@ -45134,18 +46014,27 @@
         <v>14.6558695901769</v>
       </c>
       <c r="FS253" s="16"/>
-      <c r="FV253"/>
+      <c r="FV253" s="16">
+        <v>14.6558695901769</v>
+      </c>
       <c r="FW253"/>
       <c r="FX253"/>
       <c r="FY253"/>
+      <c r="FZ253"/>
+      <c r="GA253"/>
+      <c r="GB253"/>
+      <c r="GC253"/>
     </row>
-    <row r="254" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FV254"/>
+    <row r="254" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="FW254"/>
       <c r="FX254"/>
       <c r="FY254"/>
+      <c r="FZ254"/>
+      <c r="GA254"/>
+      <c r="GB254"/>
+      <c r="GC254"/>
     </row>
-    <row r="255" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="8"/>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
@@ -45317,12 +46206,16 @@
       <c r="FO255" s="8"/>
       <c r="FR255" s="8"/>
       <c r="FS255" s="8"/>
-      <c r="FV255"/>
+      <c r="FV255" s="8"/>
       <c r="FW255"/>
       <c r="FX255"/>
       <c r="FY255"/>
+      <c r="FZ255"/>
+      <c r="GA255"/>
+      <c r="GB255"/>
+      <c r="GC255"/>
     </row>
-    <row r="256" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>0</v>
       </c>
@@ -45332,35 +46225,47 @@
       <c r="FQ256" s="4"/>
       <c r="FT256" s="4"/>
       <c r="FU256" s="4"/>
-      <c r="FV256"/>
       <c r="FW256"/>
       <c r="FX256"/>
       <c r="FY256"/>
+      <c r="FZ256"/>
+      <c r="GA256"/>
+      <c r="GB256"/>
+      <c r="GC256"/>
     </row>
-    <row r="257" spans="1:181" ht="15" x14ac:dyDescent="0.25">
-      <c r="FV257"/>
+    <row r="257" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FW257"/>
       <c r="FX257"/>
       <c r="FY257"/>
+      <c r="FZ257"/>
+      <c r="GA257"/>
+      <c r="GB257"/>
+      <c r="GC257"/>
     </row>
-    <row r="258" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FU258"/>
-      <c r="FV258"/>
       <c r="FW258"/>
       <c r="FX258"/>
       <c r="FY258"/>
+      <c r="FZ258"/>
+      <c r="GA258"/>
+      <c r="GB258"/>
+      <c r="GC258"/>
     </row>
-    <row r="259" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>8</v>
       </c>
       <c r="FU259"/>
-      <c r="FV259"/>
       <c r="FW259"/>
       <c r="FX259"/>
       <c r="FY259"/>
+      <c r="FZ259"/>
+      <c r="GA259"/>
+      <c r="GB259"/>
+      <c r="GC259"/>
     </row>
-    <row r="260" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>7</v>
       </c>
@@ -45369,29 +46274,33 @@
       <c r="FW260"/>
       <c r="FX260"/>
       <c r="FY260"/>
+      <c r="FZ260"/>
+      <c r="GA260"/>
+      <c r="GB260"/>
+      <c r="GC260"/>
     </row>
-    <row r="261" spans="1:181" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>41</v>
       </c>
       <c r="FU261"/>
     </row>
-    <row r="263" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="264" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="265" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="267" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="5">
         <v>1981</v>
@@ -45663,8 +46572,14 @@
       <c r="FW267" s="5"/>
       <c r="FX267" s="5"/>
       <c r="FY267" s="5"/>
+      <c r="FZ267" s="5">
+        <v>2024</v>
+      </c>
+      <c r="GA267" s="5"/>
+      <c r="GB267" s="5"/>
+      <c r="GC267" s="5"/>
     </row>
-    <row r="268" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
         <v>13</v>
       </c>
@@ -46208,8 +47123,20 @@
       <c r="FY268" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ268" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA268" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB268" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC268" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="270" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A270" s="12" t="s">
         <v>36</v>
       </c>
@@ -46753,8 +47680,20 @@
       <c r="FY270" s="11">
         <v>8.7226479388170546</v>
       </c>
+      <c r="FZ270" s="11">
+        <v>8.9185310328990344</v>
+      </c>
+      <c r="GA270" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB270" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC270" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="271" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A271" s="12" t="s">
         <v>37</v>
       </c>
@@ -47298,8 +48237,20 @@
       <c r="FY271" s="11">
         <v>27.528532839547044</v>
       </c>
+      <c r="FZ271" s="11">
+        <v>27.628248316679933</v>
+      </c>
+      <c r="GA271" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB271" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC271" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="272" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A272" s="12" t="s">
         <v>38</v>
       </c>
@@ -47843,8 +48794,20 @@
       <c r="FY272" s="11">
         <v>63.748819221635898</v>
       </c>
+      <c r="FZ272" s="11">
+        <v>63.453220650421038</v>
+      </c>
+      <c r="GA272" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB272" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC272" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="273" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A273" s="14"/>
       <c r="B273" s="11"/>
       <c r="C273" s="11"/>
@@ -48026,8 +48989,12 @@
       <c r="FW273" s="11"/>
       <c r="FX273" s="11"/>
       <c r="FY273" s="11"/>
+      <c r="FZ273" s="11"/>
+      <c r="GA273" s="11"/>
+      <c r="GB273" s="11"/>
+      <c r="GC273" s="11"/>
     </row>
-    <row r="274" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A274" s="7" t="s">
         <v>10</v>
       </c>
@@ -48571,8 +49538,20 @@
       <c r="FY274" s="11">
         <v>100</v>
       </c>
+      <c r="FZ274" s="11">
+        <v>100</v>
+      </c>
+      <c r="GA274" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB274" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC274" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="275" spans="1:181" s="13" customFormat="1" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:185" s="13" customFormat="1" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="FB275" s="13">
         <v>20558.222744577564</v>
@@ -48581,10 +49560,10 @@
         <v>-24370.119758612476</v>
       </c>
     </row>
-    <row r="276" spans="1:181" s="13" customFormat="1" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:185" s="13" customFormat="1" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
     </row>
-    <row r="277" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB277" s="1">
         <v>4422950.8840171499</v>
       </c>
@@ -48592,8 +49571,8 @@
         <v>4857262.3839106075</v>
       </c>
     </row>
-    <row r="278" spans="1:181" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="8"/>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
@@ -48775,49 +49754,54 @@
       <c r="FW279" s="8"/>
       <c r="FX279" s="8"/>
       <c r="FY279" s="8"/>
+      <c r="FZ279" s="8"/>
+      <c r="GA279" s="8"/>
+      <c r="GB279" s="8"/>
+      <c r="GC279" s="8"/>
     </row>
-    <row r="280" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="284" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="287" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="288" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A288" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="289" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="290" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:185" x14ac:dyDescent="0.2">
       <c r="FJ290" s="8"/>
       <c r="FN290" s="8"/>
       <c r="FR290" s="8"/>
       <c r="FV290" s="8"/>
+      <c r="FZ290" s="8"/>
     </row>
-    <row r="291" spans="1:181" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:185" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="5">
         <v>1981</v>
@@ -49089,8 +50073,14 @@
       <c r="FW291" s="5"/>
       <c r="FX291" s="5"/>
       <c r="FY291" s="5"/>
+      <c r="FZ291" s="5">
+        <v>2025</v>
+      </c>
+      <c r="GA291" s="5"/>
+      <c r="GB291" s="5"/>
+      <c r="GC291" s="5"/>
     </row>
-    <row r="292" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
         <v>13</v>
       </c>
@@ -49634,8 +50624,20 @@
       <c r="FY292" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="FZ292" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA292" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB292" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="GC292" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="294" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A294" s="12" t="s">
         <v>36</v>
       </c>
@@ -50179,8 +51181,20 @@
       <c r="FY294" s="11">
         <v>8.2856100615363282</v>
       </c>
+      <c r="FZ294" s="11">
+        <v>8.099242873004421</v>
+      </c>
+      <c r="GA294" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB294" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC294" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="295" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A295" s="12" t="s">
         <v>37</v>
       </c>
@@ -50724,8 +51738,20 @@
       <c r="FY295" s="11">
         <v>28.615970870943681</v>
       </c>
+      <c r="FZ295" s="11">
+        <v>28.734685619238331</v>
+      </c>
+      <c r="GA295" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB295" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC295" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="296" spans="1:181" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A296" s="12" t="s">
         <v>38</v>
       </c>
@@ -51269,8 +52295,20 @@
       <c r="FY296" s="11">
         <v>63.098419067519998</v>
       </c>
+      <c r="FZ296" s="11">
+        <v>63.166071507757252</v>
+      </c>
+      <c r="GA296" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB296" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC296" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="297" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A297" s="14"/>
       <c r="B297" s="11"/>
       <c r="C297" s="11"/>
@@ -51452,8 +52490,12 @@
       <c r="FW297" s="11"/>
       <c r="FX297" s="11"/>
       <c r="FY297" s="11"/>
+      <c r="FZ297" s="11"/>
+      <c r="GA297" s="11"/>
+      <c r="GB297" s="11"/>
+      <c r="GC297" s="11"/>
     </row>
-    <row r="298" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A298" s="7" t="s">
         <v>10</v>
       </c>
@@ -51997,8 +53039,20 @@
       <c r="FY298" s="11">
         <v>100</v>
       </c>
+      <c r="FZ298" s="11">
+        <v>100</v>
+      </c>
+      <c r="GA298" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GB298" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="GC298" s="11" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
-    <row r="299" spans="1:181" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:185" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB299" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -52006,7 +53060,7 @@
         <v>-0.58654919688841323</v>
       </c>
     </row>
-    <row r="300" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB300" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -52014,7 +53068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB301" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -52022,7 +53076,7 @@
         <v>116.90641566717015</v>
       </c>
     </row>
-    <row r="302" spans="1:181" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:185" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="FB302" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -52030,7 +53084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:181" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:185" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="8"/>
       <c r="B303" s="8"/>
       <c r="C303" s="8"/>
@@ -52212,71 +53266,85 @@
       <c r="FW303" s="8"/>
       <c r="FX303" s="8"/>
       <c r="FY303" s="8"/>
+      <c r="FZ303" s="8"/>
+      <c r="GA303" s="8"/>
+      <c r="GB303" s="8"/>
+      <c r="GC303" s="8"/>
     </row>
-    <row r="304" spans="1:181" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:185" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B147:BY147 CA147:FY147">
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="B147:BY147 CA147:GC147">
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B294:BY294 CA294:FY294">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="B294:BY294 CA294:GC294">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66:FU73">
-    <cfRule type="cellIs" dxfId="9" priority="14" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="B66:FV73">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93:FU100">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="B93:FV100">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222:FU226">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="B222:FV226">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B246:FU250">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThanOrEqual">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B120:FY127">
-    <cfRule type="cellIs" dxfId="5" priority="12" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="B246:FV250">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148:FY154">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThanOrEqual">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B270:FY274">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="14" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B295:FY298">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="11" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B120:GC127">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B270:GC274">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZ147:FY151">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZ294:FY296">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FZ147:GC154">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="FZ294:GC298">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/National Accounts/PSA-Quarter-Q1-1981-to-latest.xlsx
+++ b/Data/National Accounts/PSA-Quarter-Q1-1981-to-latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP 1981 and 1946 series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP 1981 and 1946 series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE49FFD-230A-4DE1-A59E-A0D6629F1E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ED9C67-EA46-480F-A27C-A0002FBADA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="721" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="87">
   <si>
     <t>Source: Philippine Statistics Authority</t>
   </si>
@@ -229,13 +229,13 @@
     <t>3. Services</t>
   </si>
   <si>
-    <t>Q1 1981 to Q1 2026</t>
+    <t>Q1 1981 to Q2 2026</t>
   </si>
   <si>
-    <t>Q1 1982 to Q1 2026</t>
+    <t>Q1 1982 to Q2 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
     <t>1981 - 1982</t>
@@ -1004,8 +1004,8 @@
     <col min="162" max="162" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="163" max="164" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="165" max="165" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="166" max="182" width="15" style="1" customWidth="1"/>
-    <col min="183" max="185" width="15" style="1" hidden="1" customWidth="1"/>
+    <col min="166" max="183" width="15" style="1" customWidth="1"/>
+    <col min="184" max="185" width="15" style="1" hidden="1" customWidth="1"/>
     <col min="186" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
@@ -2420,10 +2420,10 @@
         <v>6043627.9269005563</v>
       </c>
       <c r="FZ12" s="6">
-        <v>5452905.1588575263</v>
+        <v>5453720.281844751</v>
       </c>
       <c r="GA12" s="6">
-        <v>0</v>
+        <v>5487098.6561622685</v>
       </c>
       <c r="GB12" s="6">
         <v>0</v>
@@ -2980,7 +2980,7 @@
         <v>1057919.7254915542</v>
       </c>
       <c r="GA13" s="6">
-        <v>0</v>
+        <v>1353733.3670198247</v>
       </c>
       <c r="GB13" s="6">
         <v>0</v>
@@ -3534,10 +3534,10 @@
         <v>1455570.2933898694</v>
       </c>
       <c r="FZ14" s="6">
-        <v>1450530.0602415975</v>
+        <v>1456742.7998483218</v>
       </c>
       <c r="GA14" s="6">
-        <v>0</v>
+        <v>1737779.1876398248</v>
       </c>
       <c r="GB14" s="6">
         <v>0</v>
@@ -4091,10 +4091,10 @@
         <v>1994661.2692439985</v>
       </c>
       <c r="FZ15" s="6">
-        <v>2067891.5134642548</v>
+        <v>2067436.6410409159</v>
       </c>
       <c r="GA15" s="6">
-        <v>0</v>
+        <v>2031724.7651086687</v>
       </c>
       <c r="GB15" s="6">
         <v>0</v>
@@ -4648,10 +4648,10 @@
         <v>2693583.9508949714</v>
       </c>
       <c r="FZ16" s="6">
-        <v>3111449.2745340024</v>
+        <v>3131078.2109714886</v>
       </c>
       <c r="GA16" s="6">
-        <v>0</v>
+        <v>3164744.1094880681</v>
       </c>
       <c r="GB16" s="6">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>46899.07625182718</v>
       </c>
       <c r="FZ17" s="6">
-        <v>16134.475405740552</v>
+        <v>31128.708178349771</v>
       </c>
       <c r="GA17" s="6">
-        <v>0</v>
+        <v>37864.475080716424</v>
       </c>
       <c r="GB17" s="6">
         <v>0</v>
@@ -5948,10 +5948,10 @@
         <v>7907139.537660352</v>
       </c>
       <c r="FZ19" s="6">
-        <v>6933931.6589266723</v>
+        <v>6935869.9454324041</v>
       </c>
       <c r="GA19" s="6">
-        <v>0</v>
+        <v>7483456.3415232347</v>
       </c>
       <c r="GB19" s="6">
         <v>0</v>
@@ -7567,10 +7567,10 @@
         <v>4805972.1092409659</v>
       </c>
       <c r="FZ39" s="6">
-        <v>4192515.5066607129</v>
+        <v>4193012.0073280982</v>
       </c>
       <c r="GA39" s="6">
-        <v>0</v>
+        <v>4062196.1651612697</v>
       </c>
       <c r="GB39" s="6">
         <v>0</v>
@@ -8127,7 +8127,7 @@
         <v>916516.90179032064</v>
       </c>
       <c r="GA40" s="6">
-        <v>0</v>
+        <v>1109219.3681823406</v>
       </c>
       <c r="GB40" s="6">
         <v>0</v>
@@ -8681,10 +8681,10 @@
         <v>1265208.0699194246</v>
       </c>
       <c r="FZ41" s="6">
-        <v>1164109.6302006533</v>
+        <v>1167063.3389452279</v>
       </c>
       <c r="GA41" s="6">
-        <v>0</v>
+        <v>1380880.4938994998</v>
       </c>
       <c r="GB41" s="6">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>1629144.7244439216</v>
       </c>
       <c r="FZ42" s="6">
-        <v>1713777.8223234387</v>
+        <v>1714641.1738954908</v>
       </c>
       <c r="GA42" s="6">
-        <v>0</v>
+        <v>1737506.9769493849</v>
       </c>
       <c r="GB42" s="6">
         <v>0</v>
@@ -9795,10 +9795,10 @@
         <v>2103560.8293640027</v>
       </c>
       <c r="FZ43" s="6">
-        <v>2374729.9355641338</v>
+        <v>2388974.5241333731</v>
       </c>
       <c r="GA43" s="6">
-        <v>0</v>
+        <v>2313594.7390907863</v>
       </c>
       <c r="GB43" s="6">
         <v>0</v>
@@ -10352,16 +10352,16 @@
         <v>14845.693796754815</v>
       </c>
       <c r="FZ44" s="6">
-        <v>14771.212075891905</v>
+        <v>28629.788922225125</v>
       </c>
       <c r="GA44" s="6">
-        <v>0</v>
+        <v>2015.0007662009448</v>
       </c>
       <c r="GB44" s="6">
-        <v>0</v>
+        <v>1.0358128690735804</v>
       </c>
       <c r="GC44" s="6">
-        <v>0</v>
+        <v>5903.0771524179654</v>
       </c>
     </row>
     <row r="45" spans="1:185" x14ac:dyDescent="0.2">
@@ -11095,16 +11095,16 @@
         <v>6382257.0769706834</v>
       </c>
       <c r="FZ46" s="6">
-        <v>5626961.1374868834</v>
+        <v>5630888.6867479896</v>
       </c>
       <c r="GA46" s="6">
-        <v>0</v>
+        <v>5978223.2658679103</v>
       </c>
       <c r="GB46" s="6">
-        <v>0</v>
+        <v>1.0358128690735804</v>
       </c>
       <c r="GC46" s="6">
-        <v>0</v>
+        <v>5903.0771524179654</v>
       </c>
     </row>
     <row r="47" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -11742,7 +11742,7 @@
       <c r="FV63" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="FW63"/>
+      <c r="FW63" s="5"/>
       <c r="FZ63"/>
       <c r="GA63"/>
     </row>
@@ -12281,7 +12281,9 @@
       <c r="FV64" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="FW64"/>
+      <c r="FW64" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="FZ64"/>
       <c r="GA64"/>
     </row>
@@ -12460,7 +12462,7 @@
       <c r="FS65" s="9"/>
       <c r="FU65" s="4"/>
       <c r="FV65" s="9"/>
-      <c r="FW65"/>
+      <c r="FW65" s="9"/>
       <c r="FZ65"/>
       <c r="GA65"/>
     </row>
@@ -12997,9 +12999,11 @@
         <v>5.4505627561364491</v>
       </c>
       <c r="FV66" s="11">
-        <v>5.8501992776329246</v>
-      </c>
-      <c r="FW66"/>
+        <v>5.8660222065340974</v>
+      </c>
+      <c r="FW66" s="11">
+        <v>9.2548995137978096</v>
+      </c>
       <c r="FZ66"/>
       <c r="GA66"/>
     </row>
@@ -13538,7 +13542,9 @@
       <c r="FV67" s="11">
         <v>7.9445657207995168</v>
       </c>
-      <c r="FW67"/>
+      <c r="FW67" s="11">
+        <v>14.565504749670438</v>
+      </c>
       <c r="FZ67"/>
       <c r="GA67"/>
     </row>
@@ -14075,9 +14081,11 @@
         <v>-10.329177002742313</v>
       </c>
       <c r="FV68" s="11">
-        <v>-1.1473611227701355</v>
-      </c>
-      <c r="FW68"/>
+        <v>-0.72396713624392817</v>
+      </c>
+      <c r="FW68" s="11">
+        <v>-4.2069904384633929</v>
+      </c>
       <c r="FZ68"/>
       <c r="GA68"/>
     </row>
@@ -14614,9 +14622,11 @@
         <v>14.357164947053874</v>
       </c>
       <c r="FV69" s="11">
-        <v>11.005065248055914</v>
-      </c>
-      <c r="FW69"/>
+        <v>10.980647553653881</v>
+      </c>
+      <c r="FW69" s="11">
+        <v>20.535805119978363</v>
+      </c>
       <c r="FZ69"/>
       <c r="GA69"/>
     </row>
@@ -15153,9 +15163,11 @@
         <v>3.953309514959912</v>
       </c>
       <c r="FV70" s="11">
-        <v>8.8774754111588692</v>
-      </c>
-      <c r="FW70"/>
+        <v>9.5643415162280974</v>
+      </c>
+      <c r="FW70" s="11">
+        <v>16.015028509983864</v>
+      </c>
       <c r="FZ70"/>
       <c r="GA70"/>
     </row>
@@ -15337,7 +15349,7 @@
       <c r="FT71" s="11"/>
       <c r="FU71" s="11"/>
       <c r="FV71" s="11"/>
-      <c r="FW71"/>
+      <c r="FW71" s="11"/>
       <c r="FZ71"/>
       <c r="GA71"/>
     </row>
@@ -15519,7 +15531,7 @@
       <c r="FT72" s="11"/>
       <c r="FU72" s="11"/>
       <c r="FV72" s="11"/>
-      <c r="FW72"/>
+      <c r="FW72" s="11"/>
       <c r="FZ72"/>
       <c r="GA72"/>
     </row>
@@ -16056,29 +16068,27 @@
         <v>4.3231271264010616</v>
       </c>
       <c r="FV73" s="11">
-        <v>5.3235350852525869</v>
-      </c>
-      <c r="FW73"/>
+        <v>5.3529768503049979</v>
+      </c>
+      <c r="FW73" s="11">
+        <v>7.4731218671970652</v>
+      </c>
       <c r="FZ73"/>
       <c r="GA73"/>
     </row>
     <row r="74" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW74"/>
       <c r="FZ74"/>
       <c r="GA74"/>
     </row>
     <row r="75" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW75"/>
       <c r="FZ75"/>
       <c r="GA75"/>
     </row>
     <row r="76" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW76"/>
       <c r="FZ76"/>
       <c r="GA76"/>
     </row>
     <row r="77" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW77"/>
       <c r="FZ77"/>
       <c r="GA77"/>
     </row>
@@ -16258,7 +16268,7 @@
       <c r="FS78" s="8"/>
       <c r="FT78" s="8"/>
       <c r="FV78" s="8"/>
-      <c r="FW78"/>
+      <c r="FW78" s="8"/>
       <c r="FZ78"/>
       <c r="GA78"/>
     </row>
@@ -16269,7 +16279,6 @@
       <c r="FM79" s="4"/>
       <c r="FQ79" s="4"/>
       <c r="FU79" s="4"/>
-      <c r="FW79"/>
       <c r="FZ79"/>
       <c r="GA79"/>
     </row>
@@ -16277,12 +16286,10 @@
       <c r="A80" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="FW80"/>
       <c r="FZ80"/>
       <c r="GA80"/>
     </row>
     <row r="81" spans="1:183" ht="15" x14ac:dyDescent="0.25">
-      <c r="FW81"/>
       <c r="FZ81"/>
       <c r="GA81"/>
     </row>
@@ -16290,7 +16297,6 @@
       <c r="A82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="FW82"/>
       <c r="FZ82"/>
       <c r="GA82"/>
     </row>
@@ -16298,7 +16304,6 @@
       <c r="A83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="FW83"/>
       <c r="FZ83"/>
       <c r="GA83"/>
     </row>
@@ -16306,12 +16311,10 @@
       <c r="A84" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="FW84"/>
       <c r="FZ84"/>
       <c r="GA84"/>
     </row>
     <row r="85" spans="1:183" ht="15" x14ac:dyDescent="0.25">
-      <c r="FW85"/>
       <c r="FZ85"/>
       <c r="GA85"/>
     </row>
@@ -16319,7 +16322,6 @@
       <c r="A86" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="FW86"/>
       <c r="FZ86"/>
       <c r="GA86"/>
     </row>
@@ -16327,7 +16329,6 @@
       <c r="A87" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="FW87"/>
       <c r="FZ87"/>
       <c r="GA87"/>
     </row>
@@ -16335,7 +16336,6 @@
       <c r="A88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="FW88"/>
       <c r="FZ88"/>
       <c r="GA88"/>
     </row>
@@ -16422,7 +16422,6 @@
       <c r="FC89" s="8"/>
       <c r="FF89" s="8"/>
       <c r="FG89" s="8"/>
-      <c r="FW89"/>
       <c r="FZ89"/>
       <c r="GA89"/>
     </row>
@@ -16695,7 +16694,7 @@
       <c r="FV90" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="FW90"/>
+      <c r="FW90" s="5"/>
       <c r="FZ90"/>
       <c r="GA90"/>
     </row>
@@ -17234,7 +17233,9 @@
       <c r="FV91" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="FW91"/>
+      <c r="FW91" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="FZ91"/>
       <c r="GA91"/>
     </row>
@@ -17413,7 +17414,7 @@
       <c r="FS92" s="9"/>
       <c r="FU92" s="4"/>
       <c r="FV92" s="9"/>
-      <c r="FW92"/>
+      <c r="FW92" s="9"/>
       <c r="FZ92"/>
       <c r="GA92"/>
     </row>
@@ -17950,9 +17951,11 @@
         <v>3.7778645631406675</v>
       </c>
       <c r="FV93" s="11">
-        <v>3.0158187478206173</v>
-      </c>
-      <c r="FW93"/>
+        <v>3.0280184457533608</v>
+      </c>
+      <c r="FW93" s="11">
+        <v>2.8319698099088129</v>
+      </c>
       <c r="FZ93"/>
       <c r="GA93"/>
     </row>
@@ -18491,7 +18494,9 @@
       <c r="FV94" s="11">
         <v>4.8204556176628444</v>
       </c>
-      <c r="FW94"/>
+      <c r="FW94" s="11">
+        <v>8.3346762691940626</v>
+      </c>
       <c r="FZ94"/>
       <c r="GA94"/>
     </row>
@@ -19028,9 +19033,11 @@
         <v>-9.3793290080509166</v>
       </c>
       <c r="FV95" s="11">
-        <v>-3.3358050659838057</v>
-      </c>
-      <c r="FW95"/>
+        <v>-3.0905378931534955</v>
+      </c>
+      <c r="FW95" s="11">
+        <v>-9.187691526616419</v>
+      </c>
       <c r="FZ95"/>
       <c r="GA95"/>
     </row>
@@ -19567,9 +19574,11 @@
         <v>13.331483611044789</v>
       </c>
       <c r="FV96" s="11">
-        <v>7.785515528806954</v>
-      </c>
-      <c r="FW96"/>
+        <v>7.8398147460474235</v>
+      </c>
+      <c r="FW96" s="11">
+        <v>12.199572918100188</v>
+      </c>
       <c r="FZ96"/>
       <c r="GA96"/>
     </row>
@@ -20106,9 +20115,11 @@
         <v>3.2284956644134581</v>
       </c>
       <c r="FV97" s="11">
-        <v>6.1432002062635149</v>
-      </c>
-      <c r="FW97"/>
+        <v>6.7798899593665141</v>
+      </c>
+      <c r="FW97" s="11">
+        <v>5.4747852143553786</v>
+      </c>
       <c r="FZ97"/>
       <c r="GA97"/>
     </row>
@@ -20290,7 +20301,7 @@
       <c r="FT98" s="11"/>
       <c r="FU98" s="11"/>
       <c r="FV98" s="11"/>
-      <c r="FW98"/>
+      <c r="FW98" s="11"/>
       <c r="FZ98"/>
       <c r="GA98"/>
     </row>
@@ -20472,7 +20483,7 @@
       <c r="FT99" s="11"/>
       <c r="FU99" s="11"/>
       <c r="FV99" s="11"/>
-      <c r="FW99"/>
+      <c r="FW99" s="11"/>
       <c r="FZ99"/>
       <c r="GA99"/>
     </row>
@@ -21009,29 +21020,27 @@
         <v>3.0153928557466827</v>
       </c>
       <c r="FV100" s="11">
-        <v>2.7581741121167624</v>
-      </c>
-      <c r="FW100"/>
+        <v>2.8298980463941774</v>
+      </c>
+      <c r="FW100" s="11">
+        <v>2.33558210320885</v>
+      </c>
       <c r="FZ100"/>
       <c r="GA100"/>
     </row>
     <row r="101" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW101"/>
       <c r="FZ101"/>
       <c r="GA101"/>
     </row>
     <row r="102" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW102"/>
       <c r="FZ102"/>
       <c r="GA102"/>
     </row>
     <row r="103" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW103"/>
       <c r="FZ103"/>
       <c r="GA103"/>
     </row>
     <row r="104" spans="1:183" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW104"/>
       <c r="FZ104"/>
       <c r="GA104"/>
     </row>
@@ -21208,7 +21217,7 @@
       <c r="FR105" s="8"/>
       <c r="FS105" s="8"/>
       <c r="FV105" s="8"/>
-      <c r="FW105"/>
+      <c r="FW105" s="8"/>
       <c r="FZ105"/>
       <c r="GA105"/>
     </row>
@@ -21222,7 +21231,6 @@
       <c r="FQ106" s="4"/>
       <c r="FT106" s="4"/>
       <c r="FU106" s="4"/>
-      <c r="FW106"/>
       <c r="FZ106"/>
       <c r="GA106"/>
     </row>
@@ -21231,13 +21239,11 @@
         <v>21</v>
       </c>
       <c r="FV107"/>
-      <c r="FW107"/>
       <c r="FZ107"/>
       <c r="GA107"/>
     </row>
     <row r="108" spans="1:183" ht="15" x14ac:dyDescent="0.25">
       <c r="FV108"/>
-      <c r="FW108"/>
       <c r="FZ108"/>
       <c r="GA108"/>
     </row>
@@ -22652,10 +22658,10 @@
         <v>76.432544260990852</v>
       </c>
       <c r="FZ120" s="11">
-        <v>78.640884091170875</v>
-      </c>
-      <c r="GA120" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>78.630659524351103</v>
+      </c>
+      <c r="GA120" s="11">
+        <v>73.323052955038506</v>
       </c>
       <c r="GB120" s="11" t="e">
         <v>#DIV/0!</v>
@@ -23209,10 +23215,10 @@
         <v>13.405162735786311</v>
       </c>
       <c r="FZ121" s="11">
-        <v>15.257140934315371</v>
-      </c>
-      <c r="GA121" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>15.252877199467157</v>
+      </c>
+      <c r="GA121" s="11">
+        <v>18.089680827138714</v>
       </c>
       <c r="GB121" s="11" t="e">
         <v>#DIV/0!</v>
@@ -23766,10 +23772,10 @@
         <v>18.408304121322729</v>
       </c>
       <c r="FZ122" s="11">
-        <v>20.919301365974672</v>
-      </c>
-      <c r="GA122" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>21.003029343242737</v>
+      </c>
+      <c r="GA122" s="11">
+        <v>23.221611890717668</v>
       </c>
       <c r="GB122" s="11" t="e">
         <v>#DIV/0!</v>
@@ -24323,10 +24329,10 @@
         <v>25.226079035835504</v>
       </c>
       <c r="FZ123" s="11">
-        <v>29.822784751592877</v>
-      </c>
-      <c r="GA123" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>29.807892265950287</v>
+      </c>
+      <c r="GA123" s="11">
+        <v>27.149550587143768</v>
       </c>
       <c r="GB123" s="11" t="e">
         <v>#DIV/0!</v>
@@ -24880,10 +24886,10 @@
         <v>34.065213318493903</v>
       </c>
       <c r="FZ124" s="11">
-        <v>44.872799842616772</v>
-      </c>
-      <c r="GA124" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>45.143265885967928</v>
+      </c>
+      <c r="GA124" s="11">
+        <v>42.289872019803809</v>
       </c>
       <c r="GB124" s="11" t="e">
         <v>#DIV/0!</v>
@@ -25811,8 +25817,8 @@
       <c r="FZ127" s="11">
         <v>100</v>
       </c>
-      <c r="GA127" s="11" t="e">
-        <v>#DIV/0!</v>
+      <c r="GA127" s="11">
+        <v>100</v>
       </c>
       <c r="GB127" s="11" t="e">
         <v>#DIV/0!</v>
@@ -27444,16 +27450,16 @@
         <v>75.302076542521604</v>
       </c>
       <c r="FZ147" s="11">
-        <v>74.50763216987805</v>
-      </c>
-      <c r="GA147" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB147" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC147" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>74.464480485933578</v>
+      </c>
+      <c r="GA147" s="11">
+        <v>67.949890536106068</v>
+      </c>
+      <c r="GB147" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC147" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:185" x14ac:dyDescent="0.2">
@@ -28001,16 +28007,16 @@
         <v>12.074839663140052</v>
       </c>
       <c r="FZ148" s="11">
-        <v>16.287955068402265</v>
-      </c>
-      <c r="GA148" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB148" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC148" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>16.276594207008507</v>
+      </c>
+      <c r="GA148" s="11">
+        <v>18.55433159405942</v>
+      </c>
+      <c r="GB148" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC148" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:185" x14ac:dyDescent="0.2">
@@ -28558,16 +28564,16 @@
         <v>19.823834337302365</v>
       </c>
       <c r="FZ149" s="11">
-        <v>20.688069488259671</v>
-      </c>
-      <c r="GA149" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB149" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC149" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>20.726095006847714</v>
+      </c>
+      <c r="GA149" s="11">
+        <v>23.098509916541659</v>
+      </c>
+      <c r="GB149" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC149" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:185" x14ac:dyDescent="0.2">
@@ -29115,16 +29121,16 @@
         <v>25.526153283960003</v>
       </c>
       <c r="FZ150" s="11">
-        <v>30.45654271372571</v>
-      </c>
-      <c r="GA150" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB150" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC150" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>30.450631672595691</v>
+      </c>
+      <c r="GA150" s="11">
+        <v>29.063935883250018</v>
+      </c>
+      <c r="GB150" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC150" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:185" x14ac:dyDescent="0.2">
@@ -29672,16 +29678,16 @@
         <v>32.959512661349123</v>
       </c>
       <c r="FZ151" s="11">
-        <v>42.20270724358933</v>
-      </c>
-      <c r="GA151" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB151" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC151" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>42.426243121369154</v>
+      </c>
+      <c r="GA151" s="11">
+        <v>38.700373609330256</v>
+      </c>
+      <c r="GB151" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC151" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:185" x14ac:dyDescent="0.2">
@@ -30603,14 +30609,14 @@
       <c r="FZ154" s="11">
         <v>100</v>
       </c>
-      <c r="GA154" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB154" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC154" s="11" t="e">
-        <v>#DIV/0!</v>
+      <c r="GA154" s="11">
+        <v>100</v>
+      </c>
+      <c r="GB154" s="11">
+        <v>100</v>
+      </c>
+      <c r="GC154" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="155" spans="1:185" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -32220,10 +32226,10 @@
         <v>689711.94390111906</v>
       </c>
       <c r="FZ174" s="6">
-        <v>618404.8468013861</v>
+        <v>616464.94342981884</v>
       </c>
       <c r="GA174" s="6">
-        <v>0</v>
+        <v>573756.56754699419</v>
       </c>
       <c r="GB174" s="6">
         <v>0</v>
@@ -32777,10 +32783,10 @@
         <v>2176719.5042936383</v>
       </c>
       <c r="FZ175" s="6">
-        <v>1915723.8568371453</v>
+        <v>1917824.7084787684</v>
       </c>
       <c r="GA175" s="6">
-        <v>0</v>
+        <v>2039324.5779289799</v>
       </c>
       <c r="GB175" s="6">
         <v>0</v>
@@ -33334,10 +33340,10 @@
         <v>5040708.0894655949</v>
       </c>
       <c r="FZ176" s="6">
-        <v>4399802.955288141</v>
+        <v>4401580.2935238164</v>
       </c>
       <c r="GA176" s="6">
-        <v>0</v>
+        <v>4870375.1960472604</v>
       </c>
       <c r="GB176" s="6">
         <v>0</v>
@@ -34078,10 +34084,10 @@
         <v>7907139.537660352</v>
       </c>
       <c r="FZ178" s="6">
-        <v>6933931.6589266723</v>
+        <v>6935869.9454324041</v>
       </c>
       <c r="GA178" s="6">
-        <v>0</v>
+        <v>7483456.3415232347</v>
       </c>
       <c r="GB178" s="6">
         <v>0</v>
@@ -35717,10 +35723,10 @@
         <v>528808.93452259735</v>
       </c>
       <c r="FZ198" s="6">
-        <v>455741.24889463489</v>
+        <v>455263.03570798878</v>
       </c>
       <c r="GA198" s="6">
-        <v>0</v>
+        <v>448278.45158153359</v>
       </c>
       <c r="GB198" s="6">
         <v>0</v>
@@ -36274,16 +36280,16 @@
         <v>1826344.8260546725</v>
       </c>
       <c r="FZ199" s="6">
-        <v>1616889.592773573</v>
+        <v>1618631.3591216772</v>
       </c>
       <c r="GA199" s="6">
-        <v>0</v>
+        <v>1668522.3681580392</v>
       </c>
       <c r="GB199" s="6">
-        <v>0</v>
+        <v>1.0358128690735804</v>
       </c>
       <c r="GC199" s="6">
-        <v>0</v>
+        <v>5903.0771524179654</v>
       </c>
     </row>
     <row r="200" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
@@ -36831,10 +36837,10 @@
         <v>4027103.316393414</v>
       </c>
       <c r="FZ200" s="6">
-        <v>3554330.2958186753</v>
+        <v>3556994.2919183234</v>
       </c>
       <c r="GA200" s="6">
-        <v>0</v>
+        <v>3861422.4461283376</v>
       </c>
       <c r="GB200" s="6">
         <v>0</v>
@@ -37575,16 +37581,16 @@
         <v>6382257.0769706834</v>
       </c>
       <c r="FZ202" s="6">
-        <v>5626961.1374868834</v>
+        <v>5630888.6867479896</v>
       </c>
       <c r="GA202" s="6">
-        <v>0</v>
+        <v>5978223.2658679103</v>
       </c>
       <c r="GB202" s="6">
-        <v>0</v>
+        <v>1.0358128690735804</v>
       </c>
       <c r="GC202" s="6">
-        <v>0</v>
+        <v>5903.0771524179654</v>
       </c>
     </row>
     <row r="203" spans="1:185" s="13" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -38013,7 +38019,6 @@
       <c r="FL218" s="8"/>
       <c r="FP218" s="8"/>
       <c r="FT218" s="8"/>
-      <c r="FW218"/>
       <c r="FX218"/>
       <c r="FY218"/>
       <c r="FZ218"/>
@@ -38290,7 +38295,7 @@
       <c r="FV219" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="FW219"/>
+      <c r="FW219" s="5"/>
       <c r="FX219"/>
       <c r="FY219"/>
       <c r="FZ219"/>
@@ -38833,7 +38838,9 @@
       <c r="FV220" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="FW220"/>
+      <c r="FW220" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="FX220"/>
       <c r="FY220"/>
       <c r="FZ220"/>
@@ -38896,7 +38903,7 @@
       <c r="FT221" s="4"/>
       <c r="FU221" s="4"/>
       <c r="FV221" s="9"/>
-      <c r="FW221"/>
+      <c r="FW221" s="9"/>
       <c r="FX221"/>
       <c r="FY221"/>
       <c r="FZ221"/>
@@ -39437,9 +39444,11 @@
         <v>-2.0499984234648139</v>
       </c>
       <c r="FV222" s="11">
-        <v>-1.3730581800920305</v>
-      </c>
-      <c r="FW222"/>
+        <v>-1.6824456920971613</v>
+      </c>
+      <c r="FW222" s="11">
+        <v>1.7830872175274237</v>
+      </c>
       <c r="FX222"/>
       <c r="FY222"/>
       <c r="FZ222"/>
@@ -39980,9 +39989,11 @@
         <v>0.6458671007052601</v>
       </c>
       <c r="FV223" s="11">
-        <v>3.2644679009770812</v>
-      </c>
-      <c r="FW223"/>
+        <v>3.3777114282927982</v>
+      </c>
+      <c r="FW223" s="11">
+        <v>3.04000203128534</v>
+      </c>
       <c r="FX223"/>
       <c r="FY223"/>
       <c r="FZ223"/>
@@ -40523,9 +40534,11 @@
         <v>6.9630053219279233</v>
       </c>
       <c r="FV224" s="11">
-        <v>7.2787195409626833</v>
-      </c>
-      <c r="FW224"/>
+        <v>7.3220557021617623</v>
+      </c>
+      <c r="FW224" s="11">
+        <v>10.183691437001173</v>
+      </c>
       <c r="FX224"/>
       <c r="FY224"/>
       <c r="FZ224"/>
@@ -40712,7 +40725,7 @@
       <c r="FT225" s="11"/>
       <c r="FU225" s="11"/>
       <c r="FV225" s="11"/>
-      <c r="FW225"/>
+      <c r="FW225" s="11"/>
       <c r="FX225"/>
       <c r="FY225"/>
       <c r="FZ225"/>
@@ -41253,9 +41266,11 @@
         <v>4.3231271264010616</v>
       </c>
       <c r="FV226" s="11">
-        <v>5.3235350852525869</v>
-      </c>
-      <c r="FW226"/>
+        <v>5.3529768503049979</v>
+      </c>
+      <c r="FW226" s="11">
+        <v>7.4731218671970652</v>
+      </c>
       <c r="FX226"/>
       <c r="FY226"/>
       <c r="FZ226"/>
@@ -41439,7 +41454,7 @@
       <c r="FR227" s="16"/>
       <c r="FS227" s="16"/>
       <c r="FV227" s="16"/>
-      <c r="FW227"/>
+      <c r="FW227" s="16"/>
       <c r="FX227"/>
       <c r="FY227"/>
       <c r="FZ227"/>
@@ -41623,7 +41638,7 @@
       <c r="FR228" s="16"/>
       <c r="FS228" s="16"/>
       <c r="FV228" s="16"/>
-      <c r="FW228"/>
+      <c r="FW228" s="16"/>
       <c r="FX228"/>
       <c r="FY228"/>
       <c r="FZ228"/>
@@ -41815,7 +41830,7 @@
       <c r="FV229" s="16">
         <v>14.6558695901769</v>
       </c>
-      <c r="FW229"/>
+      <c r="FW229" s="16"/>
       <c r="FX229"/>
       <c r="FY229"/>
       <c r="FZ229"/>
@@ -41830,7 +41845,6 @@
       <c r="EY230" s="1" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="FW230"/>
       <c r="FX230"/>
       <c r="FY230"/>
       <c r="FZ230"/>
@@ -42011,7 +42025,7 @@
       <c r="FR231" s="8"/>
       <c r="FS231" s="8"/>
       <c r="FV231" s="8"/>
-      <c r="FW231"/>
+      <c r="FW231" s="8"/>
       <c r="FX231"/>
       <c r="FY231"/>
       <c r="FZ231"/>
@@ -42029,7 +42043,6 @@
       <c r="FQ232" s="4"/>
       <c r="FT232" s="4"/>
       <c r="FU232" s="4"/>
-      <c r="FW232"/>
       <c r="FX232"/>
       <c r="FY232"/>
       <c r="FZ232"/>
@@ -42038,7 +42051,6 @@
       <c r="GC232"/>
     </row>
     <row r="233" spans="1:185" ht="15" x14ac:dyDescent="0.25">
-      <c r="FW233"/>
       <c r="FX233"/>
       <c r="FY233"/>
       <c r="FZ233"/>
@@ -42047,7 +42059,6 @@
       <c r="GC233"/>
     </row>
     <row r="234" spans="1:185" ht="15" x14ac:dyDescent="0.25">
-      <c r="FW234"/>
       <c r="FX234"/>
       <c r="FY234"/>
       <c r="FZ234"/>
@@ -42059,7 +42070,6 @@
       <c r="A235" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="FW235"/>
       <c r="FX235"/>
       <c r="FY235"/>
       <c r="FZ235"/>
@@ -42071,7 +42081,6 @@
       <c r="A236" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="FW236"/>
       <c r="FX236"/>
       <c r="FY236"/>
       <c r="FZ236"/>
@@ -42083,7 +42092,6 @@
       <c r="A237" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="FW237"/>
       <c r="FX237"/>
       <c r="FY237"/>
       <c r="FZ237"/>
@@ -42092,7 +42100,6 @@
       <c r="GC237"/>
     </row>
     <row r="238" spans="1:185" ht="15" x14ac:dyDescent="0.25">
-      <c r="FW238"/>
       <c r="FX238"/>
       <c r="FY238"/>
       <c r="FZ238"/>
@@ -42104,7 +42111,6 @@
       <c r="A239" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="FW239"/>
       <c r="FX239"/>
       <c r="FY239"/>
       <c r="FZ239"/>
@@ -42116,7 +42122,6 @@
       <c r="A240" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="FW240"/>
       <c r="FX240"/>
       <c r="FY240"/>
       <c r="FZ240"/>
@@ -42128,7 +42133,6 @@
       <c r="A241" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="FW241"/>
       <c r="FX241"/>
       <c r="FY241"/>
       <c r="FZ241"/>
@@ -42222,7 +42226,6 @@
       <c r="FL242" s="8"/>
       <c r="FP242" s="8"/>
       <c r="FT242" s="8"/>
-      <c r="FW242"/>
       <c r="FX242"/>
       <c r="FY242"/>
       <c r="FZ242"/>
@@ -42499,7 +42502,7 @@
       <c r="FV243" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="FW243"/>
+      <c r="FW243" s="5"/>
       <c r="FX243"/>
       <c r="FY243"/>
       <c r="FZ243"/>
@@ -43042,7 +43045,9 @@
       <c r="FV244" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="FW244"/>
+      <c r="FW244" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="FX244"/>
       <c r="FY244"/>
       <c r="FZ244"/>
@@ -43102,7 +43107,7 @@
       <c r="FS245" s="9"/>
       <c r="FU245" s="4"/>
       <c r="FV245" s="9"/>
-      <c r="FW245"/>
+      <c r="FW245" s="9"/>
       <c r="FX245"/>
       <c r="FY245"/>
       <c r="FZ245"/>
@@ -43643,9 +43648,11 @@
         <v>1.0256262320668554</v>
       </c>
       <c r="FV246" s="11">
-        <v>-0.20950936020631161</v>
-      </c>
-      <c r="FW246"/>
+        <v>-0.31422037471635633</v>
+      </c>
+      <c r="FW246" s="11">
+        <v>2.7003314368928955</v>
+      </c>
       <c r="FX246"/>
       <c r="FY246"/>
       <c r="FZ246"/>
@@ -44186,9 +44193,11 @@
         <v>-0.30910505893317008</v>
       </c>
       <c r="FV247" s="11">
-        <v>-5.0285569020928733E-2</v>
-      </c>
-      <c r="FW247"/>
+        <v>5.7383532120283576E-2</v>
+      </c>
+      <c r="FW247" s="11">
+        <v>-2.408900724260036</v>
+      </c>
       <c r="FX247"/>
       <c r="FY247"/>
       <c r="FZ247"/>
@@ -44729,9 +44738,11 @@
         <v>4.8726960835999478</v>
       </c>
       <c r="FV248" s="11">
-        <v>4.4922757672596987</v>
-      </c>
-      <c r="FW248"/>
+        <v>4.5705934788732918</v>
+      </c>
+      <c r="FW248" s="11">
+        <v>4.4874658518384365</v>
+      </c>
       <c r="FX248"/>
       <c r="FY248"/>
       <c r="FZ248"/>
@@ -44918,7 +44929,7 @@
       <c r="FT249" s="11"/>
       <c r="FU249" s="11"/>
       <c r="FV249" s="11"/>
-      <c r="FW249"/>
+      <c r="FW249" s="11"/>
       <c r="FX249"/>
       <c r="FY249"/>
       <c r="FZ249"/>
@@ -45459,9 +45470,11 @@
         <v>3.0153928557466827</v>
       </c>
       <c r="FV250" s="11">
-        <v>2.7581741121167624</v>
-      </c>
-      <c r="FW250"/>
+        <v>2.8298980463941774</v>
+      </c>
+      <c r="FW250" s="11">
+        <v>2.33558210320885</v>
+      </c>
       <c r="FX250"/>
       <c r="FY250"/>
       <c r="FZ250"/>
@@ -45645,7 +45658,7 @@
       <c r="FR251" s="16"/>
       <c r="FS251" s="16"/>
       <c r="FV251" s="16"/>
-      <c r="FW251"/>
+      <c r="FW251" s="16"/>
       <c r="FX251"/>
       <c r="FY251"/>
       <c r="FZ251"/>
@@ -45825,7 +45838,7 @@
       <c r="FR252" s="16"/>
       <c r="FS252" s="16"/>
       <c r="FV252" s="16"/>
-      <c r="FW252"/>
+      <c r="FW252" s="16"/>
       <c r="FX252"/>
       <c r="FY252"/>
       <c r="FZ252"/>
@@ -46017,7 +46030,7 @@
       <c r="FV253" s="16">
         <v>14.6558695901769</v>
       </c>
-      <c r="FW253"/>
+      <c r="FW253" s="16"/>
       <c r="FX253"/>
       <c r="FY253"/>
       <c r="FZ253"/>
@@ -46026,7 +46039,6 @@
       <c r="GC253"/>
     </row>
     <row r="254" spans="1:185" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="FW254"/>
       <c r="FX254"/>
       <c r="FY254"/>
       <c r="FZ254"/>
@@ -46207,7 +46219,7 @@
       <c r="FR255" s="8"/>
       <c r="FS255" s="8"/>
       <c r="FV255" s="8"/>
-      <c r="FW255"/>
+      <c r="FW255" s="8"/>
       <c r="FX255"/>
       <c r="FY255"/>
       <c r="FZ255"/>
@@ -46225,7 +46237,6 @@
       <c r="FQ256" s="4"/>
       <c r="FT256" s="4"/>
       <c r="FU256" s="4"/>
-      <c r="FW256"/>
       <c r="FX256"/>
       <c r="FY256"/>
       <c r="FZ256"/>
@@ -46234,7 +46245,6 @@
       <c r="GC256"/>
     </row>
     <row r="257" spans="1:185" ht="15" x14ac:dyDescent="0.25">
-      <c r="FW257"/>
       <c r="FX257"/>
       <c r="FY257"/>
       <c r="FZ257"/>
@@ -46244,7 +46254,6 @@
     </row>
     <row r="258" spans="1:185" ht="15" x14ac:dyDescent="0.25">
       <c r="FU258"/>
-      <c r="FW258"/>
       <c r="FX258"/>
       <c r="FY258"/>
       <c r="FZ258"/>
@@ -47681,10 +47690,10 @@
         <v>8.7226479388170546</v>
       </c>
       <c r="FZ270" s="11">
-        <v>8.9185310328990344</v>
-      </c>
-      <c r="GA270" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>8.8880695324425734</v>
+      </c>
+      <c r="GA270" s="11">
+        <v>7.6669995970098466</v>
       </c>
       <c r="GB270" s="11" t="e">
         <v>#DIV/0!</v>
@@ -48238,10 +48247,10 @@
         <v>27.528532839547044</v>
       </c>
       <c r="FZ271" s="11">
-        <v>27.628248316679933</v>
-      </c>
-      <c r="GA271" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>27.650817036177934</v>
+      </c>
+      <c r="GA271" s="11">
+        <v>27.25110543658068</v>
       </c>
       <c r="GB271" s="11" t="e">
         <v>#DIV/0!</v>
@@ -48795,10 +48804,10 @@
         <v>63.748819221635898</v>
       </c>
       <c r="FZ272" s="11">
-        <v>63.453220650421038</v>
-      </c>
-      <c r="GA272" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>63.461113431379488</v>
+      </c>
+      <c r="GA272" s="11">
+        <v>65.081894966409465</v>
       </c>
       <c r="GB272" s="11" t="e">
         <v>#DIV/0!</v>
@@ -49541,8 +49550,8 @@
       <c r="FZ274" s="11">
         <v>100</v>
       </c>
-      <c r="GA274" s="11" t="e">
-        <v>#DIV/0!</v>
+      <c r="GA274" s="11">
+        <v>100</v>
       </c>
       <c r="GB274" s="11" t="e">
         <v>#DIV/0!</v>
@@ -51182,16 +51191,16 @@
         <v>8.2856100615363282</v>
       </c>
       <c r="FZ294" s="11">
-        <v>8.099242873004421</v>
-      </c>
-      <c r="GA294" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB294" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC294" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>8.0851009677997574</v>
+      </c>
+      <c r="GA294" s="11">
+        <v>7.4985230836214525</v>
+      </c>
+      <c r="GB294" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC294" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
@@ -51739,16 +51748,16 @@
         <v>28.615970870943681</v>
       </c>
       <c r="FZ295" s="11">
-        <v>28.734685619238331</v>
-      </c>
-      <c r="GA295" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB295" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC295" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>28.745575506243693</v>
+      </c>
+      <c r="GA295" s="11">
+        <v>27.910004259698812</v>
+      </c>
+      <c r="GB295" s="11">
+        <v>100</v>
+      </c>
+      <c r="GC295" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="296" spans="1:185" s="13" customFormat="1" x14ac:dyDescent="0.2">
@@ -52296,16 +52305,16 @@
         <v>63.098419067519998</v>
       </c>
       <c r="FZ296" s="11">
-        <v>63.166071507757252</v>
-      </c>
-      <c r="GA296" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB296" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC296" s="11" t="e">
-        <v>#DIV/0!</v>
+        <v>63.169323525956543</v>
+      </c>
+      <c r="GA296" s="11">
+        <v>64.591472656679741</v>
+      </c>
+      <c r="GB296" s="11">
+        <v>0</v>
+      </c>
+      <c r="GC296" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:185" x14ac:dyDescent="0.2">
@@ -53042,14 +53051,14 @@
       <c r="FZ298" s="11">
         <v>100</v>
       </c>
-      <c r="GA298" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GB298" s="11" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="GC298" s="11" t="e">
-        <v>#DIV/0!</v>
+      <c r="GA298" s="11">
+        <v>100</v>
+      </c>
+      <c r="GB298" s="11">
+        <v>100</v>
+      </c>
+      <c r="GC298" s="11">
+        <v>100</v>
       </c>
     </row>
     <row r="299" spans="1:185" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -53279,72 +53288,72 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B147:BY147 CA147:GC147">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="13" priority="25" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294:BY294 CA294:GC294">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66:FV73">
+  <conditionalFormatting sqref="B66:FW73">
     <cfRule type="cellIs" dxfId="11" priority="4" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93:FV100">
+  <conditionalFormatting sqref="B93:FW100">
     <cfRule type="cellIs" dxfId="10" priority="3" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222:FV226">
+  <conditionalFormatting sqref="B222:FW226">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B246:FV250">
+  <conditionalFormatting sqref="B246:FW250">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148:FY154">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B295:FY298">
-    <cfRule type="cellIs" dxfId="6" priority="11" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120:GC127">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270:GC274">
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="13" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZ147:FY151">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="19" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BZ294:FY296">
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FZ147:GC154">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FZ294:GC298">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
